--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-02-28T11:16:02.461Z</t>
+    <t>2026-03-01T11:16:03.221Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-01T11:16:03.221Z</t>
+    <t>2026-03-02T11:16:02.950Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-02T11:16:02.950Z</t>
+    <t>2026-03-03T11:16:03.055Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-03T11:16:03.055Z</t>
+    <t>2026-03-04T11:16:02.890Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-04T11:16:02.890Z</t>
+    <t>2026-03-05T11:16:02.148Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-05T11:16:02.148Z</t>
+    <t>2026-03-06T11:16:03.386Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-06T11:16:03.386Z</t>
+    <t>2026-03-07T11:16:02.629Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-07T11:16:02.629Z</t>
+    <t>2026-03-08T11:16:03.244Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-08T11:16:03.244Z</t>
+    <t>2026-03-09T11:16:02.718Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-09T11:16:02.718Z</t>
+    <t>2026-03-10T11:16:02.583Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-10T11:16:02.583Z</t>
+    <t>2026-03-11T11:16:03.166Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-11T11:16:03.166Z</t>
+    <t>2026-03-12T11:16:03.058Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-12T11:16:03.058Z</t>
+    <t>2026-03-13T11:16:03.008Z</t>
   </si>
   <si>
     <t>Environment</t>
@@ -2116,10 +2116,10 @@
         <v>19.37</v>
       </c>
       <c r="N2" s="6">
-        <v>22.68</v>
+        <v>19.37</v>
       </c>
       <c r="O2" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P2">
         <v>1</v>
@@ -2157,7 +2157,7 @@
         <v>59</v>
       </c>
       <c r="F3" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G3" s="7">
         <v>1</v>
@@ -2169,22 +2169,22 @@
         <v>54</v>
       </c>
       <c r="J3" s="6">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
       <c r="K3" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L3" s="6">
-        <v>7.58</v>
+        <v>6.49</v>
       </c>
       <c r="M3" s="6">
-        <v>12.56</v>
+        <v>10.76</v>
       </c>
       <c r="N3" s="6">
-        <v>14.7</v>
+        <v>10.76</v>
       </c>
       <c r="O3" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P3">
         <v>1</v>
@@ -2246,10 +2246,10 @@
         <v>10.76</v>
       </c>
       <c r="N4" s="6">
-        <v>12.6</v>
+        <v>10.76</v>
       </c>
       <c r="O4" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P4">
         <v>1</v>
@@ -2311,10 +2311,10 @@
         <v>8.97</v>
       </c>
       <c r="N5" s="6">
-        <v>10.5</v>
+        <v>8.97</v>
       </c>
       <c r="O5" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P5">
         <v>1</v>
@@ -2376,10 +2376,10 @@
         <v>19.37</v>
       </c>
       <c r="N6" s="6">
-        <v>22.68</v>
+        <v>19.37</v>
       </c>
       <c r="O6" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -2441,10 +2441,10 @@
         <v>21.8</v>
       </c>
       <c r="N7" s="6">
-        <v>25.51</v>
+        <v>21.8</v>
       </c>
       <c r="O7" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P7">
         <v>1</v>
@@ -2506,10 +2506,10 @@
         <v>41.93</v>
       </c>
       <c r="N8" s="6">
-        <v>49.08</v>
+        <v>41.93</v>
       </c>
       <c r="O8" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P8">
         <v>1</v>
@@ -2571,10 +2571,10 @@
         <v>50.86</v>
       </c>
       <c r="N9" s="6">
-        <v>59.53</v>
+        <v>50.86</v>
       </c>
       <c r="O9" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -2636,10 +2636,10 @@
         <v>38.67</v>
       </c>
       <c r="N10" s="6">
-        <v>45.26</v>
+        <v>38.67</v>
       </c>
       <c r="O10" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P10">
         <v>1</v>
@@ -2701,10 +2701,10 @@
         <v>10.76</v>
       </c>
       <c r="N11" s="6">
-        <v>12.6</v>
+        <v>10.76</v>
       </c>
       <c r="O11" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P11">
         <v>1</v>
@@ -2766,10 +2766,10 @@
         <v>32.52</v>
       </c>
       <c r="N12" s="6">
-        <v>38.06</v>
+        <v>32.52</v>
       </c>
       <c r="O12" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P12">
         <v>1</v>
@@ -2831,10 +2831,10 @@
         <v>13.66</v>
       </c>
       <c r="N13" s="6">
-        <v>15.99</v>
+        <v>13.66</v>
       </c>
       <c r="O13" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P13">
         <v>1</v>
@@ -2896,10 +2896,10 @@
         <v>14.8</v>
       </c>
       <c r="N14" s="6">
-        <v>17.32</v>
+        <v>14.8</v>
       </c>
       <c r="O14" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P14">
         <v>1</v>
@@ -2961,10 +2961,10 @@
         <v>14.8</v>
       </c>
       <c r="N15" s="6">
-        <v>17.32</v>
+        <v>14.8</v>
       </c>
       <c r="O15" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P15">
         <v>1</v>
@@ -3026,10 +3026,10 @@
         <v>23.32</v>
       </c>
       <c r="N16" s="6">
-        <v>27.3</v>
+        <v>23.32</v>
       </c>
       <c r="O16" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P16">
         <v>1</v>
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -3091,10 +3091,10 @@
         <v>42.61</v>
       </c>
       <c r="N17" s="6">
-        <v>49.87</v>
+        <v>42.61</v>
       </c>
       <c r="O17" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P17">
         <v>1</v>
@@ -3156,10 +3156,10 @@
         <v>15.25</v>
       </c>
       <c r="N18" s="6">
-        <v>17.85</v>
+        <v>15.25</v>
       </c>
       <c r="O18" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P18">
         <v>1</v>
@@ -3221,10 +3221,10 @@
         <v>22.42</v>
       </c>
       <c r="N19" s="6">
-        <v>26.25</v>
+        <v>22.42</v>
       </c>
       <c r="O19" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P19">
         <v>1</v>
@@ -3242,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -3286,10 +3286,10 @@
         <v>12.56</v>
       </c>
       <c r="N20" s="6">
-        <v>14.7</v>
+        <v>12.56</v>
       </c>
       <c r="O20" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P20">
         <v>1</v>
@@ -3307,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -3351,10 +3351,10 @@
         <v>29.15</v>
       </c>
       <c r="N21" s="6">
-        <v>34.12</v>
+        <v>29.15</v>
       </c>
       <c r="O21" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P21">
         <v>1</v>
@@ -3416,10 +3416,10 @@
         <v>35.88</v>
       </c>
       <c r="N22" s="6">
-        <v>42</v>
+        <v>35.88</v>
       </c>
       <c r="O22" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P22">
         <v>1</v>
@@ -3481,10 +3481,10 @@
         <v>9.87</v>
       </c>
       <c r="N23" s="6">
-        <v>11.55</v>
+        <v>9.87</v>
       </c>
       <c r="O23" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P23">
         <v>1</v>
@@ -3546,10 +3546,10 @@
         <v>20.99</v>
       </c>
       <c r="N24" s="6">
-        <v>24.57</v>
+        <v>20.99</v>
       </c>
       <c r="O24" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P24">
         <v>1</v>
@@ -3567,7 +3567,7 @@
         <v>3</v>
       </c>
       <c r="U24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3611,10 +3611,10 @@
         <v>25.56</v>
       </c>
       <c r="N25" s="6">
-        <v>29.92</v>
+        <v>25.56</v>
       </c>
       <c r="O25" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P25">
         <v>1</v>
@@ -3676,10 +3676,10 @@
         <v>20.99</v>
       </c>
       <c r="N26" s="6">
-        <v>24.57</v>
+        <v>20.99</v>
       </c>
       <c r="O26" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P26">
         <v>1</v>
@@ -3741,10 +3741,10 @@
         <v>25.65</v>
       </c>
       <c r="N27" s="6">
-        <v>30.03</v>
+        <v>25.65</v>
       </c>
       <c r="O27" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P27">
         <v>1</v>
@@ -3806,10 +3806,10 @@
         <v>13.45</v>
       </c>
       <c r="N28" s="6">
-        <v>15.75</v>
+        <v>13.45</v>
       </c>
       <c r="O28" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P28">
         <v>1</v>
@@ -3824,7 +3824,7 @@
         <v>55</v>
       </c>
       <c r="T28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U28" t="s">
         <v>55</v>
@@ -3871,10 +3871,10 @@
         <v>19.24</v>
       </c>
       <c r="N29" s="6">
-        <v>22.52</v>
+        <v>19.24</v>
       </c>
       <c r="O29" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P29">
         <v>1</v>
@@ -3886,10 +3886,10 @@
         <v>130</v>
       </c>
       <c r="S29" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U29" t="s">
         <v>57</v>
@@ -3936,10 +3936,10 @@
         <v>39.36</v>
       </c>
       <c r="N30" s="6">
-        <v>46.07</v>
+        <v>39.36</v>
       </c>
       <c r="O30" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P30">
         <v>1</v>
@@ -4001,10 +4001,10 @@
         <v>29.74</v>
       </c>
       <c r="N31" s="6">
-        <v>34.81</v>
+        <v>29.74</v>
       </c>
       <c r="O31" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P31">
         <v>1</v>
@@ -4066,10 +4066,10 @@
         <v>9.42</v>
       </c>
       <c r="N32" s="6">
-        <v>11.02</v>
+        <v>9.42</v>
       </c>
       <c r="O32" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P32">
         <v>1</v>
@@ -4131,10 +4131,10 @@
         <v>19.91</v>
       </c>
       <c r="N33" s="6">
-        <v>23.31</v>
+        <v>19.91</v>
       </c>
       <c r="O33" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P33">
         <v>1</v>
@@ -4196,10 +4196,10 @@
         <v>21.21</v>
       </c>
       <c r="N34" s="6">
-        <v>24.83</v>
+        <v>21.21</v>
       </c>
       <c r="O34" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P34">
         <v>1</v>
@@ -4217,7 +4217,7 @@
         <v>10</v>
       </c>
       <c r="U34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -4261,10 +4261,10 @@
         <v>23.43</v>
       </c>
       <c r="N35" s="6">
-        <v>27.43</v>
+        <v>23.43</v>
       </c>
       <c r="O35" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P35">
         <v>1</v>
@@ -4326,10 +4326,10 @@
         <v>38.62</v>
       </c>
       <c r="N36" s="6">
-        <v>45.2</v>
+        <v>38.62</v>
       </c>
       <c r="O36" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P36">
         <v>1</v>
@@ -4391,10 +4391,10 @@
         <v>64.58</v>
       </c>
       <c r="N37" s="6">
-        <v>75.59</v>
+        <v>64.58</v>
       </c>
       <c r="O37" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P37">
         <v>1</v>
@@ -4409,7 +4409,7 @@
         <v>55</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U37" t="s">
         <v>55</v>
@@ -4456,10 +4456,10 @@
         <v>53.29</v>
       </c>
       <c r="N38" s="6">
-        <v>62.38</v>
+        <v>53.29</v>
       </c>
       <c r="O38" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P38">
         <v>1</v>
@@ -4474,7 +4474,7 @@
         <v>55</v>
       </c>
       <c r="T38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U38" t="s">
         <v>55</v>
@@ -4521,10 +4521,10 @@
         <v>42.71</v>
       </c>
       <c r="N39" s="6">
-        <v>49.99</v>
+        <v>42.71</v>
       </c>
       <c r="O39" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P39">
         <v>1</v>
@@ -4586,10 +4586,10 @@
         <v>37.31</v>
       </c>
       <c r="N40" s="6">
-        <v>43.68</v>
+        <v>37.31</v>
       </c>
       <c r="O40" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P40">
         <v>1</v>
@@ -4651,10 +4651,10 @@
         <v>29.15</v>
       </c>
       <c r="N41" s="6">
-        <v>34.12</v>
+        <v>29.15</v>
       </c>
       <c r="O41" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P41">
         <v>1</v>
@@ -4716,10 +4716,10 @@
         <v>13.9</v>
       </c>
       <c r="N42" s="6">
-        <v>16.27</v>
+        <v>13.9</v>
       </c>
       <c r="O42" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P42">
         <v>1</v>
@@ -4781,10 +4781,10 @@
         <v>12.83</v>
       </c>
       <c r="N43" s="6">
-        <v>15.01</v>
+        <v>12.83</v>
       </c>
       <c r="O43" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P43">
         <v>1</v>
@@ -4846,10 +4846,10 @@
         <v>22.74</v>
       </c>
       <c r="N44" s="6">
-        <v>26.62</v>
+        <v>22.74</v>
       </c>
       <c r="O44" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P44">
         <v>1</v>
@@ -4911,10 +4911,10 @@
         <v>10.76</v>
       </c>
       <c r="N45" s="6">
-        <v>12.6</v>
+        <v>10.76</v>
       </c>
       <c r="O45" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P45">
         <v>1</v>
@@ -4976,10 +4976,10 @@
         <v>23.23</v>
       </c>
       <c r="N46" s="6">
-        <v>27.19</v>
+        <v>23.23</v>
       </c>
       <c r="O46" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P46">
         <v>1</v>
@@ -5041,10 +5041,10 @@
         <v>10.76</v>
       </c>
       <c r="N47" s="6">
-        <v>12.6</v>
+        <v>10.76</v>
       </c>
       <c r="O47" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P47">
         <v>1</v>
@@ -5106,10 +5106,10 @@
         <v>34.51</v>
       </c>
       <c r="N48" s="6">
-        <v>40.4</v>
+        <v>34.51</v>
       </c>
       <c r="O48" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P48">
         <v>1</v>
@@ -5171,10 +5171,10 @@
         <v>23.32</v>
       </c>
       <c r="N49" s="6">
-        <v>27.3</v>
+        <v>23.32</v>
       </c>
       <c r="O49" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P49">
         <v>1</v>
@@ -5236,10 +5236,10 @@
         <v>13.88</v>
       </c>
       <c r="N50" s="6">
-        <v>16.24</v>
+        <v>13.88</v>
       </c>
       <c r="O50" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P50">
         <v>1</v>
@@ -5301,10 +5301,10 @@
         <v>12.83</v>
       </c>
       <c r="N51" s="6">
-        <v>15.01</v>
+        <v>12.83</v>
       </c>
       <c r="O51" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P51">
         <v>1</v>
@@ -5366,10 +5366,10 @@
         <v>32.52</v>
       </c>
       <c r="N52" s="6">
-        <v>38.06</v>
+        <v>32.52</v>
       </c>
       <c r="O52" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P52">
         <v>1</v>
@@ -5431,10 +5431,10 @@
         <v>12.78</v>
       </c>
       <c r="N53" s="6">
-        <v>14.96</v>
+        <v>12.78</v>
       </c>
       <c r="O53" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P53">
         <v>1</v>
@@ -5496,10 +5496,10 @@
         <v>8.52</v>
       </c>
       <c r="N54" s="6">
-        <v>9.97</v>
+        <v>8.52</v>
       </c>
       <c r="O54" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P54">
         <v>1</v>
@@ -5561,10 +5561,10 @@
         <v>8.52</v>
       </c>
       <c r="N55" s="6">
-        <v>9.97</v>
+        <v>8.52</v>
       </c>
       <c r="O55" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P55">
         <v>1</v>
@@ -5626,10 +5626,10 @@
         <v>10.76</v>
       </c>
       <c r="N56" s="6">
-        <v>12.6</v>
+        <v>10.76</v>
       </c>
       <c r="O56" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P56">
         <v>1</v>
@@ -5667,7 +5667,7 @@
         <v>204</v>
       </c>
       <c r="F57" s="6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G57" s="7">
         <v>1</v>
@@ -5679,22 +5679,22 @@
         <v>54</v>
       </c>
       <c r="J57" s="6">
-        <v>11.7</v>
+        <v>9.1</v>
       </c>
       <c r="K57" s="6">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L57" s="6">
-        <v>14.61</v>
+        <v>11.37</v>
       </c>
       <c r="M57" s="6">
-        <v>24.22</v>
+        <v>18.84</v>
       </c>
       <c r="N57" s="6">
-        <v>28.35</v>
+        <v>18.84</v>
       </c>
       <c r="O57" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P57">
         <v>1</v>
@@ -5732,7 +5732,7 @@
         <v>207</v>
       </c>
       <c r="F58" s="6">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="G58" s="7">
         <v>1</v>
@@ -5744,22 +5744,22 @@
         <v>54</v>
       </c>
       <c r="J58" s="6">
-        <v>10.08</v>
+        <v>7.8</v>
       </c>
       <c r="K58" s="6">
-        <v>19.38</v>
+        <v>15</v>
       </c>
       <c r="L58" s="6">
-        <v>10.49</v>
+        <v>8.12</v>
       </c>
       <c r="M58" s="6">
-        <v>17.38</v>
+        <v>13.45</v>
       </c>
       <c r="N58" s="6">
-        <v>20.34</v>
+        <v>13.45</v>
       </c>
       <c r="O58" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P58">
         <v>1</v>
@@ -5821,10 +5821,10 @@
         <v>18.84</v>
       </c>
       <c r="N59" s="6">
-        <v>22.05</v>
+        <v>18.84</v>
       </c>
       <c r="O59" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P59">
         <v>1</v>
@@ -5886,10 +5886,10 @@
         <v>44.4</v>
       </c>
       <c r="N60" s="6">
-        <v>51.97</v>
+        <v>44.4</v>
       </c>
       <c r="O60" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P60">
         <v>1</v>
@@ -5904,7 +5904,7 @@
         <v>55</v>
       </c>
       <c r="T60">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U60" t="s">
         <v>55</v>
@@ -5951,10 +5951,10 @@
         <v>39.2</v>
       </c>
       <c r="N61" s="6">
-        <v>45.88</v>
+        <v>39.2</v>
       </c>
       <c r="O61" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P61">
         <v>1</v>
@@ -5969,10 +5969,10 @@
         <v>55</v>
       </c>
       <c r="T61">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U61" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -6016,10 +6016,10 @@
         <v>33.19</v>
       </c>
       <c r="N62" s="6">
-        <v>38.85</v>
+        <v>33.19</v>
       </c>
       <c r="O62" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P62">
         <v>1</v>
@@ -6081,10 +6081,10 @@
         <v>26.8</v>
       </c>
       <c r="N63" s="6">
-        <v>31.36</v>
+        <v>26.8</v>
       </c>
       <c r="O63" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P63">
         <v>1</v>
@@ -6146,10 +6146,10 @@
         <v>57.64</v>
       </c>
       <c r="N64" s="6">
-        <v>67.47</v>
+        <v>57.64</v>
       </c>
       <c r="O64" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P64">
         <v>1</v>
@@ -6167,7 +6167,7 @@
         <v>15</v>
       </c>
       <c r="U64" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -6211,10 +6211,10 @@
         <v>48.49</v>
       </c>
       <c r="N65" s="6">
-        <v>56.76</v>
+        <v>48.49</v>
       </c>
       <c r="O65" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P65">
         <v>1</v>
@@ -6229,7 +6229,7 @@
         <v>57</v>
       </c>
       <c r="T65">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="U65" t="s">
         <v>55</v>
@@ -6276,10 +6276,10 @@
         <v>37.67</v>
       </c>
       <c r="N66" s="6">
-        <v>44.1</v>
+        <v>37.67</v>
       </c>
       <c r="O66" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P66">
         <v>1</v>
@@ -6294,7 +6294,7 @@
         <v>57</v>
       </c>
       <c r="T66">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U66" t="s">
         <v>55</v>
@@ -6341,10 +6341,10 @@
         <v>16.59</v>
       </c>
       <c r="N67" s="6">
-        <v>19.42</v>
+        <v>16.59</v>
       </c>
       <c r="O67" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P67">
         <v>1</v>
@@ -6406,10 +6406,10 @@
         <v>10.76</v>
       </c>
       <c r="N68" s="6">
-        <v>12.6</v>
+        <v>10.76</v>
       </c>
       <c r="O68" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P68">
         <v>1</v>
@@ -6471,10 +6471,10 @@
         <v>17.94</v>
       </c>
       <c r="N69" s="6">
-        <v>21</v>
+        <v>17.94</v>
       </c>
       <c r="O69" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P69">
         <v>1</v>
@@ -6536,10 +6536,10 @@
         <v>8.97</v>
       </c>
       <c r="N70" s="6">
-        <v>10.5</v>
+        <v>8.97</v>
       </c>
       <c r="O70" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P70">
         <v>1</v>
@@ -6601,10 +6601,10 @@
         <v>19.37</v>
       </c>
       <c r="N71" s="6">
-        <v>22.68</v>
+        <v>19.37</v>
       </c>
       <c r="O71" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P71">
         <v>1</v>
@@ -6666,10 +6666,10 @@
         <v>37.67</v>
       </c>
       <c r="N72" s="6">
-        <v>44.1</v>
+        <v>37.67</v>
       </c>
       <c r="O72" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P72">
         <v>1</v>
@@ -6731,10 +6731,10 @@
         <v>8.1</v>
       </c>
       <c r="N73" s="6">
-        <v>9.48</v>
+        <v>8.1</v>
       </c>
       <c r="O73" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P73">
         <v>1</v>
@@ -6746,13 +6746,13 @@
         <v>246</v>
       </c>
       <c r="S73" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T73">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U73" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -6796,10 +6796,10 @@
         <v>23.62</v>
       </c>
       <c r="N74" s="6">
-        <v>27.65</v>
+        <v>23.62</v>
       </c>
       <c r="O74" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P74">
         <v>1</v>
@@ -6861,10 +6861,10 @@
         <v>18.07</v>
       </c>
       <c r="N75" s="6">
-        <v>21.16</v>
+        <v>18.07</v>
       </c>
       <c r="O75" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P75">
         <v>1</v>
@@ -6926,10 +6926,10 @@
         <v>17.94</v>
       </c>
       <c r="N76" s="6">
-        <v>21</v>
+        <v>17.94</v>
       </c>
       <c r="O76" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P76">
         <v>1</v>
@@ -6947,7 +6947,7 @@
         <v>0</v>
       </c>
       <c r="U76" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6991,10 +6991,10 @@
         <v>32.29</v>
       </c>
       <c r="N77" s="6">
-        <v>37.8</v>
+        <v>32.29</v>
       </c>
       <c r="O77" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P77">
         <v>1</v>
@@ -7056,10 +7056,10 @@
         <v>44.85</v>
       </c>
       <c r="N78" s="6">
-        <v>52.5</v>
+        <v>44.85</v>
       </c>
       <c r="O78" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P78">
         <v>1</v>
@@ -7121,10 +7121,10 @@
         <v>11.66</v>
       </c>
       <c r="N79" s="6">
-        <v>13.65</v>
+        <v>11.66</v>
       </c>
       <c r="O79" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P79">
         <v>1</v>
@@ -7186,10 +7186,10 @@
         <v>19.29</v>
       </c>
       <c r="N80" s="6">
-        <v>22.57</v>
+        <v>19.29</v>
       </c>
       <c r="O80" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P80">
         <v>1</v>
@@ -7251,10 +7251,10 @@
         <v>54</v>
       </c>
       <c r="N81" s="6">
-        <v>63.21</v>
+        <v>54</v>
       </c>
       <c r="O81" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P81">
         <v>1</v>
@@ -7316,10 +7316,10 @@
         <v>13.01</v>
       </c>
       <c r="N82" s="6">
-        <v>15.22</v>
+        <v>13.01</v>
       </c>
       <c r="O82" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P82">
         <v>1</v>
@@ -7357,7 +7357,7 @@
         <v>270</v>
       </c>
       <c r="F83" s="6">
-        <v>17.5</v>
+        <v>13.2</v>
       </c>
       <c r="G83" s="7">
         <v>0</v>
@@ -7369,22 +7369,22 @@
         <v>80</v>
       </c>
       <c r="J83" s="6">
-        <v>11.38</v>
+        <v>8.58</v>
       </c>
       <c r="K83" s="6">
-        <v>17.5</v>
+        <v>13.2</v>
       </c>
       <c r="L83" s="6">
-        <v>9.47</v>
+        <v>7.14</v>
       </c>
       <c r="M83" s="6">
-        <v>15.7</v>
+        <v>11.84</v>
       </c>
       <c r="N83" s="6">
-        <v>18.37</v>
+        <v>11.84</v>
       </c>
       <c r="O83" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P83">
         <v>1</v>
@@ -7446,10 +7446,10 @@
         <v>17.49</v>
       </c>
       <c r="N84" s="6">
-        <v>20.47</v>
+        <v>17.49</v>
       </c>
       <c r="O84" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P84">
         <v>1</v>
@@ -7511,10 +7511,10 @@
         <v>13.9</v>
       </c>
       <c r="N85" s="6">
-        <v>16.27</v>
+        <v>13.9</v>
       </c>
       <c r="O85" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P85">
         <v>1</v>
@@ -7576,10 +7576,10 @@
         <v>17.49</v>
       </c>
       <c r="N86" s="6">
-        <v>20.47</v>
+        <v>17.49</v>
       </c>
       <c r="O86" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P86">
         <v>1</v>
@@ -7641,10 +7641,10 @@
         <v>17.49</v>
       </c>
       <c r="N87" s="6">
-        <v>20.47</v>
+        <v>17.49</v>
       </c>
       <c r="O87" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P87">
         <v>1</v>
@@ -7706,10 +7706,10 @@
         <v>19.29</v>
       </c>
       <c r="N88" s="6">
-        <v>22.57</v>
+        <v>19.29</v>
       </c>
       <c r="O88" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P88">
         <v>1</v>
@@ -7771,10 +7771,10 @@
         <v>19.29</v>
       </c>
       <c r="N89" s="6">
-        <v>22.57</v>
+        <v>19.29</v>
       </c>
       <c r="O89" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P89">
         <v>1</v>
@@ -7836,10 +7836,10 @@
         <v>14.8</v>
       </c>
       <c r="N90" s="6">
-        <v>17.32</v>
+        <v>14.8</v>
       </c>
       <c r="O90" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P90">
         <v>1</v>
@@ -7901,10 +7901,10 @@
         <v>17.94</v>
       </c>
       <c r="N91" s="6">
-        <v>21</v>
+        <v>17.94</v>
       </c>
       <c r="O91" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P91">
         <v>1</v>
@@ -7966,10 +7966,10 @@
         <v>19.29</v>
       </c>
       <c r="N92" s="6">
-        <v>22.57</v>
+        <v>19.29</v>
       </c>
       <c r="O92" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P92">
         <v>1</v>
@@ -8031,10 +8031,10 @@
         <v>16.15</v>
       </c>
       <c r="N93" s="6">
-        <v>18.9</v>
+        <v>16.15</v>
       </c>
       <c r="O93" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P93">
         <v>1</v>
@@ -8096,10 +8096,10 @@
         <v>16.15</v>
       </c>
       <c r="N94" s="6">
-        <v>18.9</v>
+        <v>16.15</v>
       </c>
       <c r="O94" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P94">
         <v>1</v>
@@ -8161,10 +8161,10 @@
         <v>17.94</v>
       </c>
       <c r="N95" s="6">
-        <v>21</v>
+        <v>17.94</v>
       </c>
       <c r="O95" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P95">
         <v>1</v>
@@ -8182,7 +8182,7 @@
         <v>4</v>
       </c>
       <c r="U95" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -8226,10 +8226,10 @@
         <v>16.15</v>
       </c>
       <c r="N96" s="6">
-        <v>18.9</v>
+        <v>16.15</v>
       </c>
       <c r="O96" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P96">
         <v>1</v>
@@ -8291,10 +8291,10 @@
         <v>13.45</v>
       </c>
       <c r="N97" s="6">
-        <v>15.75</v>
+        <v>13.45</v>
       </c>
       <c r="O97" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P97">
         <v>1</v>
@@ -8356,10 +8356,10 @@
         <v>8.07</v>
       </c>
       <c r="N98" s="6">
-        <v>9.45</v>
+        <v>8.07</v>
       </c>
       <c r="O98" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P98">
         <v>1</v>
@@ -8421,10 +8421,10 @@
         <v>17.49</v>
       </c>
       <c r="N99" s="6">
-        <v>20.47</v>
+        <v>17.49</v>
       </c>
       <c r="O99" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P99">
         <v>1</v>
@@ -8486,10 +8486,10 @@
         <v>17.94</v>
       </c>
       <c r="N100" s="6">
-        <v>21</v>
+        <v>17.94</v>
       </c>
       <c r="O100" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P100">
         <v>1</v>
@@ -8551,10 +8551,10 @@
         <v>14.8</v>
       </c>
       <c r="N101" s="6">
-        <v>17.32</v>
+        <v>14.8</v>
       </c>
       <c r="O101" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P101">
         <v>1</v>
@@ -8616,10 +8616,10 @@
         <v>9.87</v>
       </c>
       <c r="N102" s="6">
-        <v>11.55</v>
+        <v>9.87</v>
       </c>
       <c r="O102" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P102">
         <v>1</v>
@@ -8681,10 +8681,10 @@
         <v>15.25</v>
       </c>
       <c r="N103" s="6">
-        <v>17.85</v>
+        <v>15.25</v>
       </c>
       <c r="O103" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P103">
         <v>1</v>
@@ -8746,10 +8746,10 @@
         <v>17.49</v>
       </c>
       <c r="N104" s="6">
-        <v>20.47</v>
+        <v>17.49</v>
       </c>
       <c r="O104" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P104">
         <v>1</v>
@@ -8811,10 +8811,10 @@
         <v>16.15</v>
       </c>
       <c r="N105" s="6">
-        <v>18.9</v>
+        <v>16.15</v>
       </c>
       <c r="O105" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P105">
         <v>1</v>
@@ -8876,10 +8876,10 @@
         <v>10.76</v>
       </c>
       <c r="N106" s="6">
-        <v>12.6</v>
+        <v>10.76</v>
       </c>
       <c r="O106" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P106">
         <v>1</v>
@@ -8941,10 +8941,10 @@
         <v>6.28</v>
       </c>
       <c r="N107" s="6">
-        <v>7.35</v>
+        <v>6.28</v>
       </c>
       <c r="O107" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P107">
         <v>1</v>
@@ -9006,10 +9006,10 @@
         <v>8.97</v>
       </c>
       <c r="N108" s="6">
-        <v>10.5</v>
+        <v>8.97</v>
       </c>
       <c r="O108" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P108">
         <v>1</v>
@@ -9071,10 +9071,10 @@
         <v>17.94</v>
       </c>
       <c r="N109" s="6">
-        <v>21</v>
+        <v>17.94</v>
       </c>
       <c r="O109" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P109">
         <v>1</v>
@@ -9136,10 +9136,10 @@
         <v>14.8</v>
       </c>
       <c r="N110" s="6">
-        <v>17.32</v>
+        <v>14.8</v>
       </c>
       <c r="O110" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P110">
         <v>1</v>
@@ -9201,10 +9201,10 @@
         <v>14.8</v>
       </c>
       <c r="N111" s="6">
-        <v>17.32</v>
+        <v>14.8</v>
       </c>
       <c r="O111" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P111">
         <v>1</v>
@@ -9266,10 +9266,10 @@
         <v>14.8</v>
       </c>
       <c r="N112" s="6">
-        <v>17.32</v>
+        <v>14.8</v>
       </c>
       <c r="O112" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P112">
         <v>1</v>
@@ -9331,10 +9331,10 @@
         <v>17.94</v>
       </c>
       <c r="N113" s="6">
-        <v>21</v>
+        <v>17.94</v>
       </c>
       <c r="O113" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P113">
         <v>1</v>
@@ -9396,10 +9396,10 @@
         <v>17.94</v>
       </c>
       <c r="N114" s="6">
-        <v>21</v>
+        <v>17.94</v>
       </c>
       <c r="O114" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P114">
         <v>1</v>
@@ -9461,10 +9461,10 @@
         <v>13.01</v>
       </c>
       <c r="N115" s="6">
-        <v>15.22</v>
+        <v>13.01</v>
       </c>
       <c r="O115" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P115">
         <v>1</v>
@@ -9526,10 +9526,10 @@
         <v>13.01</v>
       </c>
       <c r="N116" s="6">
-        <v>15.22</v>
+        <v>13.01</v>
       </c>
       <c r="O116" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P116">
         <v>1</v>
@@ -9591,10 +9591,10 @@
         <v>13.01</v>
       </c>
       <c r="N117" s="6">
-        <v>15.22</v>
+        <v>13.01</v>
       </c>
       <c r="O117" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P117">
         <v>1</v>
@@ -9656,10 +9656,10 @@
         <v>17.94</v>
       </c>
       <c r="N118" s="6">
-        <v>21</v>
+        <v>17.94</v>
       </c>
       <c r="O118" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P118">
         <v>1</v>
@@ -9721,10 +9721,10 @@
         <v>13.45</v>
       </c>
       <c r="N119" s="6">
-        <v>15.75</v>
+        <v>13.45</v>
       </c>
       <c r="O119" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P119">
         <v>1</v>
@@ -9786,10 +9786,10 @@
         <v>17.94</v>
       </c>
       <c r="N120" s="6">
-        <v>21</v>
+        <v>17.94</v>
       </c>
       <c r="O120" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P120">
         <v>1</v>
@@ -9851,10 +9851,10 @@
         <v>17.94</v>
       </c>
       <c r="N121" s="6">
-        <v>21</v>
+        <v>17.94</v>
       </c>
       <c r="O121" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P121">
         <v>1</v>
@@ -9916,10 +9916,10 @@
         <v>21.53</v>
       </c>
       <c r="N122" s="6">
-        <v>25.2</v>
+        <v>21.53</v>
       </c>
       <c r="O122" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P122">
         <v>1</v>
@@ -9981,10 +9981,10 @@
         <v>17.94</v>
       </c>
       <c r="N123" s="6">
-        <v>21</v>
+        <v>17.94</v>
       </c>
       <c r="O123" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P123">
         <v>1</v>
@@ -9996,10 +9996,10 @@
         <v>366</v>
       </c>
       <c r="S123" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U123" t="s">
         <v>55</v>
@@ -10046,10 +10046,10 @@
         <v>8.97</v>
       </c>
       <c r="N124" s="6">
-        <v>10.5</v>
+        <v>8.97</v>
       </c>
       <c r="O124" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P124">
         <v>1</v>
@@ -10061,10 +10061,10 @@
         <v>366</v>
       </c>
       <c r="S124" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U124" t="s">
         <v>55</v>
@@ -10111,10 +10111,10 @@
         <v>14.35</v>
       </c>
       <c r="N125" s="6">
-        <v>16.8</v>
+        <v>14.35</v>
       </c>
       <c r="O125" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P125">
         <v>1</v>
@@ -10132,7 +10132,7 @@
         <v>2</v>
       </c>
       <c r="U125" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
@@ -10176,10 +10176,10 @@
         <v>8.97</v>
       </c>
       <c r="N126" s="6">
-        <v>10.5</v>
+        <v>8.97</v>
       </c>
       <c r="O126" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P126">
         <v>1</v>
@@ -10197,7 +10197,7 @@
         <v>2</v>
       </c>
       <c r="U126" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
@@ -10241,10 +10241,10 @@
         <v>19.73</v>
       </c>
       <c r="N127" s="6">
-        <v>23.1</v>
+        <v>19.73</v>
       </c>
       <c r="O127" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P127">
         <v>1</v>
@@ -10306,10 +10306,10 @@
         <v>17.94</v>
       </c>
       <c r="N128" s="6">
-        <v>21</v>
+        <v>17.94</v>
       </c>
       <c r="O128" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P128">
         <v>1</v>
@@ -10371,10 +10371,10 @@
         <v>17.94</v>
       </c>
       <c r="N129" s="6">
-        <v>21</v>
+        <v>17.94</v>
       </c>
       <c r="O129" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P129">
         <v>1</v>
@@ -10436,10 +10436,10 @@
         <v>14.89</v>
       </c>
       <c r="N130" s="6">
-        <v>17.43</v>
+        <v>14.89</v>
       </c>
       <c r="O130" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P130">
         <v>1</v>
@@ -10501,10 +10501,10 @@
         <v>18.63</v>
       </c>
       <c r="N131" s="6">
-        <v>21.81</v>
+        <v>18.63</v>
       </c>
       <c r="O131" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P131">
         <v>1</v>
@@ -10566,10 +10566,10 @@
         <v>19.63</v>
       </c>
       <c r="N132" s="6">
-        <v>22.97</v>
+        <v>19.63</v>
       </c>
       <c r="O132" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P132">
         <v>1</v>
@@ -10631,10 +10631,10 @@
         <v>17.25</v>
       </c>
       <c r="N133" s="6">
-        <v>20.19</v>
+        <v>17.25</v>
       </c>
       <c r="O133" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P133">
         <v>1</v>
@@ -10696,10 +10696,10 @@
         <v>19.63</v>
       </c>
       <c r="N134" s="6">
-        <v>22.97</v>
+        <v>19.63</v>
       </c>
       <c r="O134" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P134">
         <v>1</v>
@@ -10761,10 +10761,10 @@
         <v>14.89</v>
       </c>
       <c r="N135" s="6">
-        <v>17.43</v>
+        <v>14.89</v>
       </c>
       <c r="O135" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P135">
         <v>1</v>
@@ -10826,10 +10826,10 @@
         <v>18.63</v>
       </c>
       <c r="N136" s="6">
-        <v>21.81</v>
+        <v>18.63</v>
       </c>
       <c r="O136" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P136">
         <v>1</v>
@@ -10891,10 +10891,10 @@
         <v>19.63</v>
       </c>
       <c r="N137" s="6">
-        <v>22.98</v>
+        <v>19.63</v>
       </c>
       <c r="O137" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P137">
         <v>1</v>
@@ -10956,10 +10956,10 @@
         <v>14.89</v>
       </c>
       <c r="N138" s="6">
-        <v>17.43</v>
+        <v>14.89</v>
       </c>
       <c r="O138" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P138">
         <v>1</v>
@@ -11021,10 +11021,10 @@
         <v>17.25</v>
       </c>
       <c r="N139" s="6">
-        <v>20.19</v>
+        <v>17.25</v>
       </c>
       <c r="O139" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P139">
         <v>1</v>
@@ -11086,10 +11086,10 @@
         <v>19.63</v>
       </c>
       <c r="N140" s="6">
-        <v>22.97</v>
+        <v>19.63</v>
       </c>
       <c r="O140" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P140">
         <v>1</v>
@@ -11151,10 +11151,10 @@
         <v>12.11</v>
       </c>
       <c r="N141" s="6">
-        <v>14.17</v>
+        <v>12.11</v>
       </c>
       <c r="O141" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P141">
         <v>1</v>
@@ -11216,10 +11216,10 @@
         <v>13.45</v>
       </c>
       <c r="N142" s="6">
-        <v>15.75</v>
+        <v>13.45</v>
       </c>
       <c r="O142" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P142">
         <v>1</v>
@@ -11281,10 +11281,10 @@
         <v>13.8</v>
       </c>
       <c r="N143" s="6">
-        <v>16.15</v>
+        <v>13.8</v>
       </c>
       <c r="O143" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P143">
         <v>1</v>
@@ -11346,10 +11346,10 @@
         <v>8.28</v>
       </c>
       <c r="N144" s="6">
-        <v>9.69</v>
+        <v>8.28</v>
       </c>
       <c r="O144" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P144">
         <v>1</v>
@@ -11411,10 +11411,10 @@
         <v>12.42</v>
       </c>
       <c r="N145" s="6">
-        <v>14.54</v>
+        <v>12.42</v>
       </c>
       <c r="O145" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P145">
         <v>1</v>
@@ -11476,10 +11476,10 @@
         <v>20.33</v>
       </c>
       <c r="N146" s="6">
-        <v>23.79</v>
+        <v>20.33</v>
       </c>
       <c r="O146" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P146">
         <v>1</v>
@@ -11541,10 +11541,10 @@
         <v>17.25</v>
       </c>
       <c r="N147" s="6">
-        <v>20.19</v>
+        <v>17.25</v>
       </c>
       <c r="O147" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P147">
         <v>1</v>
@@ -11606,10 +11606,10 @@
         <v>18.63</v>
       </c>
       <c r="N148" s="6">
-        <v>21.81</v>
+        <v>18.63</v>
       </c>
       <c r="O148" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P148">
         <v>1</v>
@@ -11671,10 +11671,10 @@
         <v>26.57</v>
       </c>
       <c r="N149" s="6">
-        <v>31.1</v>
+        <v>26.57</v>
       </c>
       <c r="O149" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P149">
         <v>1</v>
@@ -11736,10 +11736,10 @@
         <v>29.32</v>
       </c>
       <c r="N150" s="6">
-        <v>34.32</v>
+        <v>29.32</v>
       </c>
       <c r="O150" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P150">
         <v>1</v>
@@ -11801,10 +11801,10 @@
         <v>20.7</v>
       </c>
       <c r="N151" s="6">
-        <v>24.23</v>
+        <v>20.7</v>
       </c>
       <c r="O151" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P151">
         <v>1</v>
@@ -11866,10 +11866,10 @@
         <v>19.32</v>
       </c>
       <c r="N152" s="6">
-        <v>22.62</v>
+        <v>19.32</v>
       </c>
       <c r="O152" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P152">
         <v>1</v>
@@ -11931,10 +11931,10 @@
         <v>15.18</v>
       </c>
       <c r="N153" s="6">
-        <v>17.76</v>
+        <v>15.18</v>
       </c>
       <c r="O153" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P153">
         <v>1</v>
@@ -11996,10 +11996,10 @@
         <v>13.8</v>
       </c>
       <c r="N154" s="6">
-        <v>16.15</v>
+        <v>13.8</v>
       </c>
       <c r="O154" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P154">
         <v>1</v>
@@ -12061,10 +12061,10 @@
         <v>13.8</v>
       </c>
       <c r="N155" s="6">
-        <v>16.15</v>
+        <v>13.8</v>
       </c>
       <c r="O155" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P155">
         <v>1</v>
@@ -12126,10 +12126,10 @@
         <v>13.8</v>
       </c>
       <c r="N156" s="6">
-        <v>16.15</v>
+        <v>13.8</v>
       </c>
       <c r="O156" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P156">
         <v>1</v>
@@ -12191,10 +12191,10 @@
         <v>8</v>
       </c>
       <c r="N157" s="6">
-        <v>9.37</v>
+        <v>8</v>
       </c>
       <c r="O157" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P157">
         <v>1</v>
@@ -12256,10 +12256,10 @@
         <v>16.56</v>
       </c>
       <c r="N158" s="6">
-        <v>19.38</v>
+        <v>16.56</v>
       </c>
       <c r="O158" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P158">
         <v>1</v>
@@ -12321,10 +12321,10 @@
         <v>9.66</v>
       </c>
       <c r="N159" s="6">
-        <v>11.31</v>
+        <v>9.66</v>
       </c>
       <c r="O159" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P159">
         <v>1</v>
@@ -12386,10 +12386,10 @@
         <v>16.56</v>
       </c>
       <c r="N160" s="6">
-        <v>19.38</v>
+        <v>16.56</v>
       </c>
       <c r="O160" s="8">
-        <v>0.0499</v>
+        <v>-0.103</v>
       </c>
       <c r="P160">
         <v>1</v>
@@ -12455,7 +12455,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0.94</v>
+        <v>0.6574</v>
       </c>
       <c r="B5" t="s">
         <v>455</v>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-13T11:16:03.008Z</t>
+    <t>2026-03-14T11:16:02.333Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-14T11:16:02.333Z</t>
+    <t>2026-03-15T11:16:03.130Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-15T11:16:03.130Z</t>
+    <t>2026-03-16T11:16:02.964Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-16T11:16:02.964Z</t>
+    <t>2026-03-17T11:16:02.658Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-17T11:16:02.658Z</t>
+    <t>2026-03-18T11:16:03.010Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-18T11:16:03.010Z</t>
+    <t>2026-03-19T11:16:02.496Z</t>
   </si>
   <si>
     <t>Environment</t>
@@ -6557,7 +6557,7 @@
         <v>3</v>
       </c>
       <c r="U70" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -6817,7 +6817,7 @@
         <v>0</v>
       </c>
       <c r="U74" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -8117,7 +8117,7 @@
         <v>0</v>
       </c>
       <c r="U94" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-19T11:16:02.496Z</t>
+    <t>2026-03-20T11:16:02.787Z</t>
   </si>
   <si>
     <t>Environment</t>
@@ -2134,10 +2134,10 @@
         <v>57</v>
       </c>
       <c r="T2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -2456,13 +2456,13 @@
         <v>68</v>
       </c>
       <c r="S7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T7">
         <v>0</v>
       </c>
       <c r="U7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -2852,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="U13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -3366,7 +3366,7 @@
         <v>109</v>
       </c>
       <c r="S21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -3434,7 +3434,7 @@
         <v>55</v>
       </c>
       <c r="T22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U22" t="s">
         <v>55</v>
@@ -3561,10 +3561,10 @@
         <v>116</v>
       </c>
       <c r="S24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U24" t="s">
         <v>57</v>
@@ -3629,7 +3629,7 @@
         <v>55</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U25" t="s">
         <v>55</v>
@@ -3821,13 +3821,13 @@
         <v>127</v>
       </c>
       <c r="S28" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U28" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -4279,7 +4279,7 @@
         <v>55</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U35" t="s">
         <v>55</v>
@@ -4341,13 +4341,13 @@
         <v>149</v>
       </c>
       <c r="S36" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U36" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -4409,7 +4409,7 @@
         <v>55</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U37" t="s">
         <v>55</v>
@@ -4474,7 +4474,7 @@
         <v>55</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U38" t="s">
         <v>55</v>
@@ -4536,10 +4536,10 @@
         <v>152</v>
       </c>
       <c r="S39" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T39">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U39" t="s">
         <v>55</v>
@@ -4666,10 +4666,10 @@
         <v>162</v>
       </c>
       <c r="S41" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T41">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U41" t="s">
         <v>57</v>
@@ -4796,13 +4796,13 @@
         <v>166</v>
       </c>
       <c r="S43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4861,13 +4861,13 @@
         <v>169</v>
       </c>
       <c r="S44" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T44">
         <v>0</v>
       </c>
       <c r="U44" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -5186,10 +5186,10 @@
         <v>183</v>
       </c>
       <c r="S49" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U49" t="s">
         <v>57</v>
@@ -5251,7 +5251,7 @@
         <v>183</v>
       </c>
       <c r="S50" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T50">
         <v>0</v>
@@ -5316,7 +5316,7 @@
         <v>187</v>
       </c>
       <c r="S51" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T51">
         <v>0</v>
@@ -5446,13 +5446,13 @@
         <v>193</v>
       </c>
       <c r="S53" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U53" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -5777,7 +5777,7 @@
         <v>0</v>
       </c>
       <c r="U58" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5901,10 +5901,10 @@
         <v>214</v>
       </c>
       <c r="S60" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T60">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U60" t="s">
         <v>55</v>
@@ -5966,10 +5966,10 @@
         <v>214</v>
       </c>
       <c r="S61" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T61">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U61" t="s">
         <v>55</v>
@@ -6096,7 +6096,7 @@
         <v>214</v>
       </c>
       <c r="S63" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T63">
         <v>0</v>
@@ -6164,7 +6164,7 @@
         <v>57</v>
       </c>
       <c r="T64">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U64" t="s">
         <v>57</v>
@@ -6294,7 +6294,7 @@
         <v>57</v>
       </c>
       <c r="T66">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U66" t="s">
         <v>55</v>
@@ -6554,10 +6554,10 @@
         <v>57</v>
       </c>
       <c r="T70">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U70" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -6746,7 +6746,7 @@
         <v>246</v>
       </c>
       <c r="S73" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T73">
         <v>3</v>
@@ -7207,7 +7207,7 @@
         <v>0</v>
       </c>
       <c r="U80" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -7269,7 +7269,7 @@
         <v>55</v>
       </c>
       <c r="T81">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U81" t="s">
         <v>55</v>
@@ -7331,10 +7331,10 @@
         <v>271</v>
       </c>
       <c r="S82" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T82">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U82" t="s">
         <v>55</v>
@@ -7461,7 +7461,7 @@
         <v>276</v>
       </c>
       <c r="S84" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T84">
         <v>0</v>
@@ -8179,10 +8179,10 @@
         <v>57</v>
       </c>
       <c r="T95">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U95" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -8247,7 +8247,7 @@
         <v>0</v>
       </c>
       <c r="U96" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -8377,7 +8377,7 @@
         <v>0</v>
       </c>
       <c r="U98" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -9541,13 +9541,13 @@
         <v>349</v>
       </c>
       <c r="S116" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T116">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U116" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -9869,10 +9869,10 @@
         <v>55</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U121" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
@@ -9996,10 +9996,10 @@
         <v>366</v>
       </c>
       <c r="S123" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T123">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U123" t="s">
         <v>55</v>
@@ -10061,10 +10061,10 @@
         <v>366</v>
       </c>
       <c r="S124" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T124">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U124" t="s">
         <v>55</v>
@@ -10126,10 +10126,10 @@
         <v>369</v>
       </c>
       <c r="S125" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T125">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U125" t="s">
         <v>55</v>
@@ -10191,10 +10191,10 @@
         <v>369</v>
       </c>
       <c r="S126" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U126" t="s">
         <v>55</v>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-20T11:16:02.787Z</t>
+    <t>2026-03-20T13:49:48.522Z</t>
   </si>
   <si>
     <t>Environment</t>
@@ -8365,7 +8365,7 @@
         <v>1</v>
       </c>
       <c r="Q98" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R98" t="s">
         <v>309</v>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="453">
   <si>
     <t>Master Pricelist - Deck Family Farm</t>
   </si>
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-20T13:49:48.522Z</t>
+    <t>2026-03-20T14:10:14.634Z</t>
   </si>
   <si>
     <t>Environment</t>
@@ -947,15 +947,6 @@
   </si>
   <si>
     <t>Description:   With a blend of our pasture-raised pork and beef, these pepperoni snack sticks are a perfect balance of spicy, smoky, and satisfying. Perfect for on the trail, the open road, or browsing your local farmer’s market!  Ingredients:   Pork, Beef, Sea Salt, Contains 2% or less of the following: Spices, Jalepeno Peppers, Yeast, Cultured Celery Powder, Paprika, Chili Powder (Chili Pepper, Salt, Spices, Garlic), Fennel Seed, Cayenne Pepper, Anise Seed, Turbinado Sugar, Granulated Garlic, Packed in Collagen.    6oz Packages  Our products come from pasture‑raised animals and are tended on pastures and forests with care. Because they are not factory‑farmed, natural variation in size, shape, weight, and flavor is expected. These differences are a hallmark of truly humane, artisanal farming.</t>
-  </si>
-  <si>
-    <t>Pepperoni stick, 6 oz (Hiker's Pepperoni)</t>
-  </si>
-  <si>
-    <t>6 oz</t>
-  </si>
-  <si>
-    <t>Our Hikers Pepperoni Sticks are a delicious, high-energy snack, perfect for ketogenic diets or outdoor adventures. Due to an unintended higher fat content in this batch, these pepperoni sticks are packed with calories, making them a great choice for hiking or backpacking. Reminiscent of traditional Native American pemmican—dried meat, tallow, berries, and spices—our pepperoni offers lots of energy in a small, portable package. While the mouthfeel may differ slightly, the rich, savory flavor remains just as wonderful as ever. Stock up for your next outing!  Our products come from pasture‑raised animals and are tended on pastures and forests with care. Because they are not factory‑farmed, natural variation in size, shape, weight, and flavor is expected. These differences are a hallmark of truly humane, artisanal farming.</t>
   </si>
   <si>
     <t>Polish Kielbasa</t>
@@ -1996,7 +1987,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U160"/>
+  <dimension ref="A1:U159"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="6" max="6" width="9" style="6" customWidth="1"/>
@@ -8317,10 +8308,10 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B98">
-        <v>858286</v>
+        <v>805682</v>
       </c>
       <c r="C98" t="s">
         <v>268</v>
@@ -8329,10 +8320,10 @@
         <v>307</v>
       </c>
       <c r="E98" t="s">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="F98" s="6">
-        <v>9</v>
+        <v>19.5</v>
       </c>
       <c r="G98" s="7">
         <v>0</v>
@@ -8344,19 +8335,19 @@
         <v>80</v>
       </c>
       <c r="J98" s="6">
-        <v>5.85</v>
+        <v>12.68</v>
       </c>
       <c r="K98" s="6">
-        <v>9</v>
+        <v>19.5</v>
       </c>
       <c r="L98" s="6">
-        <v>4.87</v>
+        <v>10.55</v>
       </c>
       <c r="M98" s="6">
-        <v>8.07</v>
+        <v>17.49</v>
       </c>
       <c r="N98" s="6">
-        <v>8.07</v>
+        <v>17.49</v>
       </c>
       <c r="O98" s="8">
         <v>-0.103</v>
@@ -8365,10 +8356,10 @@
         <v>1</v>
       </c>
       <c r="Q98" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R98" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="S98" t="s">
         <v>57</v>
@@ -8382,22 +8373,22 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B99">
-        <v>805682</v>
+        <v>805670</v>
       </c>
       <c r="C99" t="s">
         <v>268</v>
       </c>
       <c r="D99" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E99" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F99" s="6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="G99" s="7">
         <v>0</v>
@@ -8409,19 +8400,19 @@
         <v>80</v>
       </c>
       <c r="J99" s="6">
-        <v>12.68</v>
+        <v>13</v>
       </c>
       <c r="K99" s="6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="L99" s="6">
-        <v>10.55</v>
+        <v>10.82</v>
       </c>
       <c r="M99" s="6">
-        <v>17.49</v>
+        <v>17.94</v>
       </c>
       <c r="N99" s="6">
-        <v>17.49</v>
+        <v>17.94</v>
       </c>
       <c r="O99" s="8">
         <v>-0.103</v>
@@ -8433,7 +8424,7 @@
         <v>55</v>
       </c>
       <c r="R99" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S99" t="s">
         <v>57</v>
@@ -8442,27 +8433,27 @@
         <v>0</v>
       </c>
       <c r="U99" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B100">
-        <v>805670</v>
+        <v>805678</v>
       </c>
       <c r="C100" t="s">
         <v>268</v>
       </c>
       <c r="D100" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E100" t="s">
         <v>270</v>
       </c>
       <c r="F100" s="6">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="G100" s="7">
         <v>0</v>
@@ -8474,19 +8465,19 @@
         <v>80</v>
       </c>
       <c r="J100" s="6">
-        <v>13</v>
+        <v>10.72</v>
       </c>
       <c r="K100" s="6">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="L100" s="6">
-        <v>10.82</v>
+        <v>8.93</v>
       </c>
       <c r="M100" s="6">
-        <v>17.94</v>
+        <v>14.8</v>
       </c>
       <c r="N100" s="6">
-        <v>17.94</v>
+        <v>14.8</v>
       </c>
       <c r="O100" s="8">
         <v>-0.103</v>
@@ -8498,7 +8489,7 @@
         <v>55</v>
       </c>
       <c r="R100" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="S100" t="s">
         <v>57</v>
@@ -8512,46 +8503,46 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="B101">
-        <v>805678</v>
+        <v>940154</v>
       </c>
       <c r="C101" t="s">
         <v>268</v>
       </c>
       <c r="D101" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E101" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="F101" s="6">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="G101" s="7">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H101" s="7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I101" t="s">
         <v>80</v>
       </c>
       <c r="J101" s="6">
-        <v>10.72</v>
+        <v>7.15</v>
       </c>
       <c r="K101" s="6">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="L101" s="6">
-        <v>8.93</v>
+        <v>5.95</v>
       </c>
       <c r="M101" s="6">
-        <v>14.8</v>
+        <v>9.87</v>
       </c>
       <c r="N101" s="6">
-        <v>14.8</v>
+        <v>9.87</v>
       </c>
       <c r="O101" s="8">
         <v>-0.103</v>
@@ -8563,7 +8554,7 @@
         <v>55</v>
       </c>
       <c r="R101" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="S101" t="s">
         <v>57</v>
@@ -8572,51 +8563,51 @@
         <v>0</v>
       </c>
       <c r="U101" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="B102">
-        <v>940154</v>
+        <v>805687</v>
       </c>
       <c r="C102" t="s">
         <v>268</v>
       </c>
       <c r="D102" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E102" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="F102" s="6">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G102" s="7">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H102" s="7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I102" t="s">
         <v>80</v>
       </c>
       <c r="J102" s="6">
-        <v>7.15</v>
+        <v>11.05</v>
       </c>
       <c r="K102" s="6">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L102" s="6">
-        <v>5.95</v>
+        <v>9.2</v>
       </c>
       <c r="M102" s="6">
-        <v>9.87</v>
+        <v>15.25</v>
       </c>
       <c r="N102" s="6">
-        <v>9.87</v>
+        <v>15.25</v>
       </c>
       <c r="O102" s="8">
         <v>-0.103</v>
@@ -8628,7 +8619,7 @@
         <v>55</v>
       </c>
       <c r="R102" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="S102" t="s">
         <v>57</v>
@@ -8637,27 +8628,27 @@
         <v>0</v>
       </c>
       <c r="U102" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B103">
-        <v>805687</v>
+        <v>805692</v>
       </c>
       <c r="C103" t="s">
         <v>268</v>
       </c>
       <c r="D103" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E103" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F103" s="6">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="G103" s="7">
         <v>0</v>
@@ -8669,19 +8660,19 @@
         <v>80</v>
       </c>
       <c r="J103" s="6">
-        <v>11.05</v>
+        <v>12.68</v>
       </c>
       <c r="K103" s="6">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="L103" s="6">
-        <v>9.2</v>
+        <v>10.55</v>
       </c>
       <c r="M103" s="6">
-        <v>15.25</v>
+        <v>17.49</v>
       </c>
       <c r="N103" s="6">
-        <v>15.25</v>
+        <v>17.49</v>
       </c>
       <c r="O103" s="8">
         <v>-0.103</v>
@@ -8693,7 +8684,7 @@
         <v>55</v>
       </c>
       <c r="R103" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="S103" t="s">
         <v>57</v>
@@ -8707,22 +8698,22 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B104">
-        <v>805692</v>
+        <v>805694</v>
       </c>
       <c r="C104" t="s">
         <v>268</v>
       </c>
       <c r="D104" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E104" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="F104" s="6">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="G104" s="7">
         <v>0</v>
@@ -8734,19 +8725,19 @@
         <v>80</v>
       </c>
       <c r="J104" s="6">
-        <v>12.68</v>
+        <v>11.7</v>
       </c>
       <c r="K104" s="6">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="L104" s="6">
-        <v>10.55</v>
+        <v>9.74</v>
       </c>
       <c r="M104" s="6">
-        <v>17.49</v>
+        <v>16.15</v>
       </c>
       <c r="N104" s="6">
-        <v>17.49</v>
+        <v>16.15</v>
       </c>
       <c r="O104" s="8">
         <v>-0.103</v>
@@ -8758,7 +8749,7 @@
         <v>55</v>
       </c>
       <c r="R104" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="S104" t="s">
         <v>57</v>
@@ -8772,46 +8763,46 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B105">
-        <v>805694</v>
+        <v>941005</v>
       </c>
       <c r="C105" t="s">
-        <v>268</v>
+        <v>321</v>
       </c>
       <c r="D105" t="s">
         <v>322</v>
       </c>
       <c r="E105" t="s">
-        <v>288</v>
+        <v>323</v>
       </c>
       <c r="F105" s="6">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G105" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" t="s">
         <v>80</v>
       </c>
       <c r="J105" s="6">
-        <v>11.7</v>
+        <v>7.8</v>
       </c>
       <c r="K105" s="6">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L105" s="6">
-        <v>9.74</v>
+        <v>6.49</v>
       </c>
       <c r="M105" s="6">
-        <v>16.15</v>
+        <v>10.76</v>
       </c>
       <c r="N105" s="6">
-        <v>16.15</v>
+        <v>10.76</v>
       </c>
       <c r="O105" s="8">
         <v>-0.103</v>
@@ -8823,7 +8814,7 @@
         <v>55</v>
       </c>
       <c r="R105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="S105" t="s">
         <v>57</v>
@@ -8837,13 +8828,13 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B106">
-        <v>941005</v>
+        <v>805459</v>
       </c>
       <c r="C106" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D106" t="s">
         <v>325</v>
@@ -8852,31 +8843,31 @@
         <v>326</v>
       </c>
       <c r="F106" s="6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G106" s="7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H106" s="7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I106" t="s">
         <v>80</v>
       </c>
       <c r="J106" s="6">
-        <v>7.8</v>
+        <v>4.55</v>
       </c>
       <c r="K106" s="6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L106" s="6">
-        <v>6.49</v>
+        <v>3.79</v>
       </c>
       <c r="M106" s="6">
-        <v>10.76</v>
+        <v>6.28</v>
       </c>
       <c r="N106" s="6">
-        <v>10.76</v>
+        <v>6.28</v>
       </c>
       <c r="O106" s="8">
         <v>-0.103</v>
@@ -8888,7 +8879,7 @@
         <v>55</v>
       </c>
       <c r="R106" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="S106" t="s">
         <v>57</v>
@@ -8902,46 +8893,46 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="B107">
-        <v>805459</v>
+        <v>995135</v>
       </c>
       <c r="C107" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D107" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E107" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F107" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G107" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H107" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I107" t="s">
         <v>80</v>
       </c>
       <c r="J107" s="6">
-        <v>4.55</v>
+        <v>6.5</v>
       </c>
       <c r="K107" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L107" s="6">
-        <v>3.79</v>
+        <v>5.41</v>
       </c>
       <c r="M107" s="6">
-        <v>6.28</v>
+        <v>8.97</v>
       </c>
       <c r="N107" s="6">
-        <v>6.28</v>
+        <v>8.97</v>
       </c>
       <c r="O107" s="8">
         <v>-0.103</v>
@@ -8953,60 +8944,60 @@
         <v>55</v>
       </c>
       <c r="R107" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="S107" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U107" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>166</v>
+        <v>109</v>
       </c>
       <c r="B108">
-        <v>995135</v>
+        <v>900311</v>
       </c>
       <c r="C108" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="D108" t="s">
         <v>330</v>
       </c>
       <c r="E108" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F108" s="6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G108" s="7">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H108" s="7">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I108" t="s">
         <v>80</v>
       </c>
       <c r="J108" s="6">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="K108" s="6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L108" s="6">
-        <v>5.41</v>
+        <v>10.82</v>
       </c>
       <c r="M108" s="6">
-        <v>8.97</v>
+        <v>17.94</v>
       </c>
       <c r="N108" s="6">
-        <v>8.97</v>
+        <v>17.94</v>
       </c>
       <c r="O108" s="8">
         <v>-0.103</v>
@@ -9018,13 +9009,13 @@
         <v>55</v>
       </c>
       <c r="R108" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="S108" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T108">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="U108" t="s">
         <v>57</v>
@@ -9032,46 +9023,46 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B109">
-        <v>900311</v>
+        <v>840823</v>
       </c>
       <c r="C109" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D109" t="s">
         <v>333</v>
       </c>
       <c r="E109" t="s">
-        <v>334</v>
+        <v>275</v>
       </c>
       <c r="F109" s="6">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="G109" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H109" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I109" t="s">
         <v>80</v>
       </c>
       <c r="J109" s="6">
-        <v>13</v>
+        <v>10.72</v>
       </c>
       <c r="K109" s="6">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="L109" s="6">
-        <v>10.82</v>
+        <v>8.93</v>
       </c>
       <c r="M109" s="6">
-        <v>17.94</v>
+        <v>14.8</v>
       </c>
       <c r="N109" s="6">
-        <v>17.94</v>
+        <v>14.8</v>
       </c>
       <c r="O109" s="8">
         <v>-0.103</v>
@@ -9083,7 +9074,7 @@
         <v>55</v>
       </c>
       <c r="R109" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="S109" t="s">
         <v>57</v>
@@ -9092,21 +9083,21 @@
         <v>0</v>
       </c>
       <c r="U109" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B110">
-        <v>840823</v>
+        <v>913652</v>
       </c>
       <c r="C110" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D110" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E110" t="s">
         <v>275</v>
@@ -9148,7 +9139,7 @@
         <v>55</v>
       </c>
       <c r="R110" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="S110" t="s">
         <v>57</v>
@@ -9162,16 +9153,16 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B111">
-        <v>913652</v>
+        <v>913651</v>
       </c>
       <c r="C111" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D111" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E111" t="s">
         <v>275</v>
@@ -9213,7 +9204,7 @@
         <v>55</v>
       </c>
       <c r="R111" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="S111" t="s">
         <v>57</v>
@@ -9227,46 +9218,46 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B112">
-        <v>913651</v>
+        <v>816905</v>
       </c>
       <c r="C112" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D112" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E112" t="s">
-        <v>275</v>
+        <v>331</v>
       </c>
       <c r="F112" s="6">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="G112" s="7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H112" s="7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I112" t="s">
         <v>80</v>
       </c>
       <c r="J112" s="6">
-        <v>10.72</v>
+        <v>13</v>
       </c>
       <c r="K112" s="6">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="L112" s="6">
-        <v>8.93</v>
+        <v>10.82</v>
       </c>
       <c r="M112" s="6">
-        <v>14.8</v>
+        <v>17.94</v>
       </c>
       <c r="N112" s="6">
-        <v>14.8</v>
+        <v>17.94</v>
       </c>
       <c r="O112" s="8">
         <v>-0.103</v>
@@ -9278,7 +9269,7 @@
         <v>55</v>
       </c>
       <c r="R112" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="S112" t="s">
         <v>57</v>
@@ -9292,19 +9283,19 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="B113">
-        <v>816905</v>
+        <v>932132</v>
       </c>
       <c r="C113" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D113" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E113" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F113" s="6">
         <v>20</v>
@@ -9343,7 +9334,7 @@
         <v>55</v>
       </c>
       <c r="R113" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="S113" t="s">
         <v>57</v>
@@ -9352,51 +9343,51 @@
         <v>0</v>
       </c>
       <c r="U113" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="B114">
-        <v>932132</v>
+        <v>1011877</v>
       </c>
       <c r="C114" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D114" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E114" t="s">
-        <v>334</v>
+        <v>98</v>
       </c>
       <c r="F114" s="6">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="G114" s="7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H114" s="7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I114" t="s">
         <v>80</v>
       </c>
       <c r="J114" s="6">
-        <v>13</v>
+        <v>9.43</v>
       </c>
       <c r="K114" s="6">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="L114" s="6">
-        <v>10.82</v>
+        <v>7.85</v>
       </c>
       <c r="M114" s="6">
-        <v>17.94</v>
+        <v>13.01</v>
       </c>
       <c r="N114" s="6">
-        <v>17.94</v>
+        <v>13.01</v>
       </c>
       <c r="O114" s="8">
         <v>-0.103</v>
@@ -9408,7 +9399,7 @@
         <v>55</v>
       </c>
       <c r="R114" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="S114" t="s">
         <v>57</v>
@@ -9422,16 +9413,16 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B115">
-        <v>1011877</v>
+        <v>1061161</v>
       </c>
       <c r="C115" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D115" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E115" t="s">
         <v>98</v>
@@ -9473,7 +9464,7 @@
         <v>55</v>
       </c>
       <c r="R115" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="S115" t="s">
         <v>57</v>
@@ -9487,16 +9478,16 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B116">
-        <v>1061161</v>
+        <v>1019999</v>
       </c>
       <c r="C116" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D116" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E116" t="s">
         <v>98</v>
@@ -9538,7 +9529,7 @@
         <v>55</v>
       </c>
       <c r="R116" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="S116" t="s">
         <v>57</v>
@@ -9552,46 +9543,46 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>174</v>
+        <v>106</v>
       </c>
       <c r="B117">
-        <v>1019999</v>
+        <v>840822</v>
       </c>
       <c r="C117" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D117" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E117" t="s">
-        <v>98</v>
+        <v>331</v>
       </c>
       <c r="F117" s="6">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="G117" s="7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H117" s="7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I117" t="s">
         <v>80</v>
       </c>
       <c r="J117" s="6">
-        <v>9.43</v>
+        <v>13</v>
       </c>
       <c r="K117" s="6">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="L117" s="6">
-        <v>7.85</v>
+        <v>10.82</v>
       </c>
       <c r="M117" s="6">
-        <v>13.01</v>
+        <v>17.94</v>
       </c>
       <c r="N117" s="6">
-        <v>13.01</v>
+        <v>17.94</v>
       </c>
       <c r="O117" s="8">
         <v>-0.103</v>
@@ -9603,7 +9594,7 @@
         <v>55</v>
       </c>
       <c r="R117" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="S117" t="s">
         <v>57</v>
@@ -9612,51 +9603,51 @@
         <v>0</v>
       </c>
       <c r="U117" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="B118">
-        <v>840822</v>
+        <v>913653</v>
       </c>
       <c r="C118" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D118" t="s">
+        <v>351</v>
+      </c>
+      <c r="E118" t="s">
         <v>352</v>
       </c>
-      <c r="E118" t="s">
-        <v>334</v>
-      </c>
       <c r="F118" s="6">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G118" s="7">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="H118" s="7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I118" t="s">
         <v>80</v>
       </c>
       <c r="J118" s="6">
-        <v>13</v>
+        <v>9.75</v>
       </c>
       <c r="K118" s="6">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L118" s="6">
-        <v>10.82</v>
+        <v>8.12</v>
       </c>
       <c r="M118" s="6">
-        <v>17.94</v>
+        <v>13.45</v>
       </c>
       <c r="N118" s="6">
-        <v>17.94</v>
+        <v>13.45</v>
       </c>
       <c r="O118" s="8">
         <v>-0.103</v>
@@ -9682,46 +9673,46 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B119">
-        <v>913653</v>
+        <v>818963</v>
       </c>
       <c r="C119" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D119" t="s">
         <v>354</v>
       </c>
       <c r="E119" t="s">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="F119" s="6">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G119" s="7">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="H119" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I119" t="s">
         <v>80</v>
       </c>
       <c r="J119" s="6">
-        <v>9.75</v>
+        <v>13</v>
       </c>
       <c r="K119" s="6">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L119" s="6">
-        <v>8.12</v>
+        <v>10.82</v>
       </c>
       <c r="M119" s="6">
-        <v>13.45</v>
+        <v>17.94</v>
       </c>
       <c r="N119" s="6">
-        <v>13.45</v>
+        <v>17.94</v>
       </c>
       <c r="O119" s="8">
         <v>-0.103</v>
@@ -9733,7 +9724,7 @@
         <v>55</v>
       </c>
       <c r="R119" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="S119" t="s">
         <v>57</v>
@@ -9747,19 +9738,19 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B120">
-        <v>818963</v>
+        <v>871143</v>
       </c>
       <c r="C120" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D120" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E120" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F120" s="6">
         <v>20</v>
@@ -9798,13 +9789,13 @@
         <v>55</v>
       </c>
       <c r="R120" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="S120" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U120" t="s">
         <v>55</v>
@@ -9812,46 +9803,46 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B121">
-        <v>871143</v>
+        <v>913648</v>
       </c>
       <c r="C121" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D121" t="s">
+        <v>358</v>
+      </c>
+      <c r="E121" t="s">
         <v>359</v>
       </c>
-      <c r="E121" t="s">
-        <v>334</v>
-      </c>
       <c r="F121" s="6">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G121" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H121" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I121" t="s">
         <v>80</v>
       </c>
       <c r="J121" s="6">
-        <v>13</v>
+        <v>15.6</v>
       </c>
       <c r="K121" s="6">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L121" s="6">
-        <v>10.82</v>
+        <v>12.99</v>
       </c>
       <c r="M121" s="6">
-        <v>17.94</v>
+        <v>21.53</v>
       </c>
       <c r="N121" s="6">
-        <v>17.94</v>
+        <v>21.53</v>
       </c>
       <c r="O121" s="8">
         <v>-0.103</v>
@@ -9866,24 +9857,24 @@
         <v>360</v>
       </c>
       <c r="S121" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T121">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U121" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B122">
-        <v>913648</v>
+        <v>805663</v>
       </c>
       <c r="C122" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D122" t="s">
         <v>361</v>
@@ -9892,31 +9883,31 @@
         <v>362</v>
       </c>
       <c r="F122" s="6">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G122" s="7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H122" s="7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I122" t="s">
         <v>80</v>
       </c>
       <c r="J122" s="6">
-        <v>15.6</v>
+        <v>13</v>
       </c>
       <c r="K122" s="6">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L122" s="6">
-        <v>12.99</v>
+        <v>10.82</v>
       </c>
       <c r="M122" s="6">
-        <v>21.53</v>
+        <v>17.94</v>
       </c>
       <c r="N122" s="6">
-        <v>21.53</v>
+        <v>17.94</v>
       </c>
       <c r="O122" s="8">
         <v>-0.103</v>
@@ -9937,51 +9928,51 @@
         <v>0</v>
       </c>
       <c r="U122" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B123">
-        <v>805663</v>
+        <v>941045</v>
       </c>
       <c r="C123" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D123" t="s">
         <v>364</v>
       </c>
       <c r="E123" t="s">
-        <v>365</v>
+        <v>270</v>
       </c>
       <c r="F123" s="6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G123" s="7">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H123" s="7">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I123" t="s">
         <v>80</v>
       </c>
       <c r="J123" s="6">
-        <v>13</v>
+        <v>6.5</v>
       </c>
       <c r="K123" s="6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L123" s="6">
-        <v>10.82</v>
+        <v>5.41</v>
       </c>
       <c r="M123" s="6">
-        <v>17.94</v>
+        <v>8.97</v>
       </c>
       <c r="N123" s="6">
-        <v>17.94</v>
+        <v>8.97</v>
       </c>
       <c r="O123" s="8">
         <v>-0.103</v>
@@ -9993,7 +9984,7 @@
         <v>55</v>
       </c>
       <c r="R123" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="S123" t="s">
         <v>57</v>
@@ -10007,46 +9998,46 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="B124">
-        <v>941045</v>
+        <v>929464</v>
       </c>
       <c r="C124" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D124" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E124" t="s">
-        <v>270</v>
+        <v>362</v>
       </c>
       <c r="F124" s="6">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G124" s="7">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H124" s="7">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I124" t="s">
         <v>80</v>
       </c>
       <c r="J124" s="6">
-        <v>6.5</v>
+        <v>10.4</v>
       </c>
       <c r="K124" s="6">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L124" s="6">
-        <v>5.41</v>
+        <v>8.66</v>
       </c>
       <c r="M124" s="6">
-        <v>8.97</v>
+        <v>14.35</v>
       </c>
       <c r="N124" s="6">
-        <v>8.97</v>
+        <v>14.35</v>
       </c>
       <c r="O124" s="8">
         <v>-0.103</v>
@@ -10072,46 +10063,46 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B125">
-        <v>929464</v>
+        <v>805665</v>
       </c>
       <c r="C125" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D125" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E125" t="s">
-        <v>365</v>
+        <v>270</v>
       </c>
       <c r="F125" s="6">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G125" s="7">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H125" s="7">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I125" t="s">
         <v>80</v>
       </c>
       <c r="J125" s="6">
-        <v>10.4</v>
+        <v>6.5</v>
       </c>
       <c r="K125" s="6">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L125" s="6">
-        <v>8.66</v>
+        <v>5.41</v>
       </c>
       <c r="M125" s="6">
-        <v>14.35</v>
+        <v>8.97</v>
       </c>
       <c r="N125" s="6">
-        <v>14.35</v>
+        <v>8.97</v>
       </c>
       <c r="O125" s="8">
         <v>-0.103</v>
@@ -10123,7 +10114,7 @@
         <v>55</v>
       </c>
       <c r="R125" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="S125" t="s">
         <v>57</v>
@@ -10137,46 +10128,46 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B126">
-        <v>805665</v>
+        <v>900310</v>
       </c>
       <c r="C126" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D126" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E126" t="s">
-        <v>270</v>
+        <v>331</v>
       </c>
       <c r="F126" s="6">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G126" s="7">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H126" s="7">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I126" t="s">
         <v>80</v>
       </c>
       <c r="J126" s="6">
-        <v>6.5</v>
+        <v>14.3</v>
       </c>
       <c r="K126" s="6">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="L126" s="6">
-        <v>5.41</v>
+        <v>11.91</v>
       </c>
       <c r="M126" s="6">
-        <v>8.97</v>
+        <v>19.73</v>
       </c>
       <c r="N126" s="6">
-        <v>8.97</v>
+        <v>19.73</v>
       </c>
       <c r="O126" s="8">
         <v>-0.103</v>
@@ -10197,51 +10188,51 @@
         <v>0</v>
       </c>
       <c r="U126" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="B127">
-        <v>900310</v>
+        <v>1011872</v>
       </c>
       <c r="C127" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D127" t="s">
+        <v>370</v>
+      </c>
+      <c r="E127" t="s">
         <v>371</v>
       </c>
-      <c r="E127" t="s">
-        <v>334</v>
-      </c>
       <c r="F127" s="6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G127" s="7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H127" s="7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I127" t="s">
         <v>80</v>
       </c>
       <c r="J127" s="6">
-        <v>14.3</v>
+        <v>13</v>
       </c>
       <c r="K127" s="6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L127" s="6">
-        <v>11.91</v>
+        <v>10.82</v>
       </c>
       <c r="M127" s="6">
-        <v>19.73</v>
+        <v>17.94</v>
       </c>
       <c r="N127" s="6">
-        <v>19.73</v>
+        <v>17.94</v>
       </c>
       <c r="O127" s="8">
         <v>-0.103</v>
@@ -10262,33 +10253,33 @@
         <v>0</v>
       </c>
       <c r="U127" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="B128">
-        <v>1011872</v>
+        <v>913650</v>
       </c>
       <c r="C128" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D128" t="s">
         <v>373</v>
       </c>
       <c r="E128" t="s">
-        <v>374</v>
+        <v>331</v>
       </c>
       <c r="F128" s="6">
         <v>20</v>
       </c>
       <c r="G128" s="7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H128" s="7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I128" t="s">
         <v>80</v>
@@ -10318,7 +10309,7 @@
         <v>55</v>
       </c>
       <c r="R128" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="S128" t="s">
         <v>57</v>
@@ -10332,46 +10323,46 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B129">
-        <v>913650</v>
+        <v>911651</v>
       </c>
       <c r="C129" t="s">
-        <v>332</v>
+        <v>375</v>
       </c>
       <c r="D129" t="s">
         <v>376</v>
       </c>
       <c r="E129" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
       <c r="F129" s="6">
-        <v>20</v>
+        <v>16.6</v>
       </c>
       <c r="G129" s="7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H129" s="7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I129" t="s">
         <v>80</v>
       </c>
       <c r="J129" s="6">
-        <v>13</v>
+        <v>10.79</v>
       </c>
       <c r="K129" s="6">
-        <v>20</v>
+        <v>16.6</v>
       </c>
       <c r="L129" s="6">
-        <v>10.82</v>
+        <v>8.98</v>
       </c>
       <c r="M129" s="6">
-        <v>17.94</v>
+        <v>14.89</v>
       </c>
       <c r="N129" s="6">
-        <v>17.94</v>
+        <v>14.89</v>
       </c>
       <c r="O129" s="8">
         <v>-0.103</v>
@@ -10380,30 +10371,30 @@
         <v>1</v>
       </c>
       <c r="Q129" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R129" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="S129" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T129">
         <v>0</v>
       </c>
       <c r="U129" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B130">
-        <v>911651</v>
+        <v>911647</v>
       </c>
       <c r="C130" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D130" t="s">
         <v>379</v>
@@ -10412,7 +10403,7 @@
         <v>380</v>
       </c>
       <c r="F130" s="6">
-        <v>16.6</v>
+        <v>20.77</v>
       </c>
       <c r="G130" s="7">
         <v>0</v>
@@ -10424,19 +10415,19 @@
         <v>80</v>
       </c>
       <c r="J130" s="6">
-        <v>10.79</v>
+        <v>13.5</v>
       </c>
       <c r="K130" s="6">
-        <v>16.6</v>
+        <v>20.77</v>
       </c>
       <c r="L130" s="6">
-        <v>8.98</v>
+        <v>11.24</v>
       </c>
       <c r="M130" s="6">
-        <v>14.89</v>
+        <v>18.63</v>
       </c>
       <c r="N130" s="6">
-        <v>14.89</v>
+        <v>18.63</v>
       </c>
       <c r="O130" s="8">
         <v>-0.103</v>
@@ -10448,7 +10439,7 @@
         <v>57</v>
       </c>
       <c r="R130" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="S130" t="s">
         <v>55</v>
@@ -10462,22 +10453,22 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B131">
-        <v>911647</v>
+        <v>911648</v>
       </c>
       <c r="C131" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D131" t="s">
+        <v>381</v>
+      </c>
+      <c r="E131" t="s">
         <v>382</v>
       </c>
-      <c r="E131" t="s">
-        <v>383</v>
-      </c>
       <c r="F131" s="6">
-        <v>20.77</v>
+        <v>21.88</v>
       </c>
       <c r="G131" s="7">
         <v>0</v>
@@ -10489,19 +10480,19 @@
         <v>80</v>
       </c>
       <c r="J131" s="6">
-        <v>13.5</v>
+        <v>14.22</v>
       </c>
       <c r="K131" s="6">
-        <v>20.77</v>
+        <v>21.88</v>
       </c>
       <c r="L131" s="6">
-        <v>11.24</v>
+        <v>11.84</v>
       </c>
       <c r="M131" s="6">
-        <v>18.63</v>
+        <v>19.63</v>
       </c>
       <c r="N131" s="6">
-        <v>18.63</v>
+        <v>19.63</v>
       </c>
       <c r="O131" s="8">
         <v>-0.103</v>
@@ -10513,7 +10504,7 @@
         <v>57</v>
       </c>
       <c r="R131" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="S131" t="s">
         <v>55</v>
@@ -10527,22 +10518,22 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B132">
-        <v>911648</v>
+        <v>957423</v>
       </c>
       <c r="C132" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D132" t="s">
+        <v>383</v>
+      </c>
+      <c r="E132" t="s">
         <v>384</v>
       </c>
-      <c r="E132" t="s">
-        <v>385</v>
-      </c>
       <c r="F132" s="6">
-        <v>21.88</v>
+        <v>19.23</v>
       </c>
       <c r="G132" s="7">
         <v>0</v>
@@ -10554,19 +10545,19 @@
         <v>80</v>
       </c>
       <c r="J132" s="6">
-        <v>14.22</v>
+        <v>12.5</v>
       </c>
       <c r="K132" s="6">
-        <v>21.88</v>
+        <v>19.23</v>
       </c>
       <c r="L132" s="6">
-        <v>11.84</v>
+        <v>10.41</v>
       </c>
       <c r="M132" s="6">
-        <v>19.63</v>
+        <v>17.25</v>
       </c>
       <c r="N132" s="6">
-        <v>19.63</v>
+        <v>17.25</v>
       </c>
       <c r="O132" s="8">
         <v>-0.103</v>
@@ -10578,7 +10569,7 @@
         <v>57</v>
       </c>
       <c r="R132" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="S132" t="s">
         <v>55</v>
@@ -10592,13 +10583,13 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B133">
-        <v>957423</v>
+        <v>957424</v>
       </c>
       <c r="C133" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D133" t="s">
         <v>386</v>
@@ -10607,7 +10598,7 @@
         <v>387</v>
       </c>
       <c r="F133" s="6">
-        <v>19.23</v>
+        <v>21.88</v>
       </c>
       <c r="G133" s="7">
         <v>0</v>
@@ -10619,19 +10610,19 @@
         <v>80</v>
       </c>
       <c r="J133" s="6">
-        <v>12.5</v>
+        <v>14.22</v>
       </c>
       <c r="K133" s="6">
-        <v>19.23</v>
+        <v>21.88</v>
       </c>
       <c r="L133" s="6">
-        <v>10.41</v>
+        <v>11.84</v>
       </c>
       <c r="M133" s="6">
-        <v>17.25</v>
+        <v>19.63</v>
       </c>
       <c r="N133" s="6">
-        <v>17.25</v>
+        <v>19.63</v>
       </c>
       <c r="O133" s="8">
         <v>-0.103</v>
@@ -10643,7 +10634,7 @@
         <v>57</v>
       </c>
       <c r="R133" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="S133" t="s">
         <v>55</v>
@@ -10657,22 +10648,22 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B134">
-        <v>957424</v>
+        <v>936388</v>
       </c>
       <c r="C134" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D134" t="s">
+        <v>388</v>
+      </c>
+      <c r="E134" t="s">
         <v>389</v>
       </c>
-      <c r="E134" t="s">
-        <v>390</v>
-      </c>
       <c r="F134" s="6">
-        <v>21.88</v>
+        <v>16.6</v>
       </c>
       <c r="G134" s="7">
         <v>0</v>
@@ -10684,19 +10675,19 @@
         <v>80</v>
       </c>
       <c r="J134" s="6">
-        <v>14.22</v>
+        <v>10.79</v>
       </c>
       <c r="K134" s="6">
-        <v>21.88</v>
+        <v>16.6</v>
       </c>
       <c r="L134" s="6">
-        <v>11.84</v>
+        <v>8.98</v>
       </c>
       <c r="M134" s="6">
-        <v>19.63</v>
+        <v>14.89</v>
       </c>
       <c r="N134" s="6">
-        <v>19.63</v>
+        <v>14.89</v>
       </c>
       <c r="O134" s="8">
         <v>-0.103</v>
@@ -10708,7 +10699,7 @@
         <v>57</v>
       </c>
       <c r="R134" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="S134" t="s">
         <v>55</v>
@@ -10722,13 +10713,13 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B135">
-        <v>936388</v>
+        <v>936387</v>
       </c>
       <c r="C135" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D135" t="s">
         <v>391</v>
@@ -10737,7 +10728,7 @@
         <v>392</v>
       </c>
       <c r="F135" s="6">
-        <v>16.6</v>
+        <v>20.77</v>
       </c>
       <c r="G135" s="7">
         <v>0</v>
@@ -10749,19 +10740,19 @@
         <v>80</v>
       </c>
       <c r="J135" s="6">
-        <v>10.79</v>
+        <v>13.5</v>
       </c>
       <c r="K135" s="6">
-        <v>16.6</v>
+        <v>20.77</v>
       </c>
       <c r="L135" s="6">
-        <v>8.98</v>
+        <v>11.24</v>
       </c>
       <c r="M135" s="6">
-        <v>14.89</v>
+        <v>18.63</v>
       </c>
       <c r="N135" s="6">
-        <v>14.89</v>
+        <v>18.63</v>
       </c>
       <c r="O135" s="8">
         <v>-0.103</v>
@@ -10773,7 +10764,7 @@
         <v>57</v>
       </c>
       <c r="R135" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="S135" t="s">
         <v>55</v>
@@ -10787,22 +10778,22 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B136">
-        <v>936387</v>
+        <v>824228</v>
       </c>
       <c r="C136" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D136" t="s">
+        <v>393</v>
+      </c>
+      <c r="E136" t="s">
         <v>394</v>
       </c>
-      <c r="E136" t="s">
-        <v>395</v>
-      </c>
       <c r="F136" s="6">
-        <v>20.77</v>
+        <v>21.89</v>
       </c>
       <c r="G136" s="7">
         <v>0</v>
@@ -10814,19 +10805,19 @@
         <v>80</v>
       </c>
       <c r="J136" s="6">
-        <v>13.5</v>
+        <v>14.23</v>
       </c>
       <c r="K136" s="6">
-        <v>20.77</v>
+        <v>21.89</v>
       </c>
       <c r="L136" s="6">
-        <v>11.24</v>
+        <v>11.85</v>
       </c>
       <c r="M136" s="6">
-        <v>18.63</v>
+        <v>19.63</v>
       </c>
       <c r="N136" s="6">
-        <v>18.63</v>
+        <v>19.63</v>
       </c>
       <c r="O136" s="8">
         <v>-0.103</v>
@@ -10838,7 +10829,7 @@
         <v>57</v>
       </c>
       <c r="R136" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="S136" t="s">
         <v>55</v>
@@ -10852,22 +10843,22 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B137">
-        <v>824228</v>
+        <v>866256</v>
       </c>
       <c r="C137" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D137" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E137" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="F137" s="6">
-        <v>21.89</v>
+        <v>16.6</v>
       </c>
       <c r="G137" s="7">
         <v>0</v>
@@ -10879,19 +10870,19 @@
         <v>80</v>
       </c>
       <c r="J137" s="6">
-        <v>14.23</v>
+        <v>10.79</v>
       </c>
       <c r="K137" s="6">
-        <v>21.89</v>
+        <v>16.6</v>
       </c>
       <c r="L137" s="6">
-        <v>11.85</v>
+        <v>8.98</v>
       </c>
       <c r="M137" s="6">
-        <v>19.63</v>
+        <v>14.89</v>
       </c>
       <c r="N137" s="6">
-        <v>19.63</v>
+        <v>14.89</v>
       </c>
       <c r="O137" s="8">
         <v>-0.103</v>
@@ -10903,7 +10894,7 @@
         <v>57</v>
       </c>
       <c r="R137" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="S137" t="s">
         <v>55</v>
@@ -10917,22 +10908,22 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B138">
-        <v>866256</v>
+        <v>805464</v>
       </c>
       <c r="C138" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D138" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E138" t="s">
         <v>392</v>
       </c>
       <c r="F138" s="6">
-        <v>16.6</v>
+        <v>19.23</v>
       </c>
       <c r="G138" s="7">
         <v>0</v>
@@ -10944,19 +10935,19 @@
         <v>80</v>
       </c>
       <c r="J138" s="6">
-        <v>10.79</v>
+        <v>12.5</v>
       </c>
       <c r="K138" s="6">
-        <v>16.6</v>
+        <v>19.23</v>
       </c>
       <c r="L138" s="6">
-        <v>8.98</v>
+        <v>10.41</v>
       </c>
       <c r="M138" s="6">
-        <v>14.89</v>
+        <v>17.25</v>
       </c>
       <c r="N138" s="6">
-        <v>14.89</v>
+        <v>17.25</v>
       </c>
       <c r="O138" s="8">
         <v>-0.103</v>
@@ -10968,7 +10959,7 @@
         <v>57</v>
       </c>
       <c r="R138" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="S138" t="s">
         <v>55</v>
@@ -10982,22 +10973,22 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B139">
-        <v>805464</v>
+        <v>842611</v>
       </c>
       <c r="C139" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D139" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E139" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F139" s="6">
-        <v>19.23</v>
+        <v>21.88</v>
       </c>
       <c r="G139" s="7">
         <v>0</v>
@@ -11009,19 +11000,19 @@
         <v>80</v>
       </c>
       <c r="J139" s="6">
-        <v>12.5</v>
+        <v>14.22</v>
       </c>
       <c r="K139" s="6">
-        <v>19.23</v>
+        <v>21.88</v>
       </c>
       <c r="L139" s="6">
-        <v>10.41</v>
+        <v>11.84</v>
       </c>
       <c r="M139" s="6">
-        <v>17.25</v>
+        <v>19.63</v>
       </c>
       <c r="N139" s="6">
-        <v>17.25</v>
+        <v>19.63</v>
       </c>
       <c r="O139" s="8">
         <v>-0.103</v>
@@ -11033,7 +11024,7 @@
         <v>57</v>
       </c>
       <c r="R139" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="S139" t="s">
         <v>55</v>
@@ -11047,22 +11038,22 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="B140">
-        <v>842611</v>
+        <v>1015821</v>
       </c>
       <c r="C140" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D140" t="s">
+        <v>400</v>
+      </c>
+      <c r="E140" t="s">
         <v>401</v>
       </c>
-      <c r="E140" t="s">
-        <v>402</v>
-      </c>
       <c r="F140" s="6">
-        <v>21.88</v>
+        <v>13.5</v>
       </c>
       <c r="G140" s="7">
         <v>0</v>
@@ -11074,19 +11065,19 @@
         <v>80</v>
       </c>
       <c r="J140" s="6">
-        <v>14.22</v>
+        <v>8.78</v>
       </c>
       <c r="K140" s="6">
-        <v>21.88</v>
+        <v>13.5</v>
       </c>
       <c r="L140" s="6">
-        <v>11.84</v>
+        <v>7.31</v>
       </c>
       <c r="M140" s="6">
-        <v>19.63</v>
+        <v>12.11</v>
       </c>
       <c r="N140" s="6">
-        <v>19.63</v>
+        <v>12.11</v>
       </c>
       <c r="O140" s="8">
         <v>-0.103</v>
@@ -11098,27 +11089,27 @@
         <v>57</v>
       </c>
       <c r="R140" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="S140" t="s">
         <v>55</v>
       </c>
       <c r="T140">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U140" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B141">
-        <v>1015821</v>
+        <v>1015823</v>
       </c>
       <c r="C141" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D141" t="s">
         <v>403</v>
@@ -11127,7 +11118,7 @@
         <v>404</v>
       </c>
       <c r="F141" s="6">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="G141" s="7">
         <v>0</v>
@@ -11139,19 +11130,19 @@
         <v>80</v>
       </c>
       <c r="J141" s="6">
-        <v>8.78</v>
+        <v>9.75</v>
       </c>
       <c r="K141" s="6">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="L141" s="6">
-        <v>7.31</v>
+        <v>8.12</v>
       </c>
       <c r="M141" s="6">
-        <v>12.11</v>
+        <v>13.45</v>
       </c>
       <c r="N141" s="6">
-        <v>12.11</v>
+        <v>13.45</v>
       </c>
       <c r="O141" s="8">
         <v>-0.103</v>
@@ -11163,13 +11154,13 @@
         <v>57</v>
       </c>
       <c r="R141" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="S141" t="s">
         <v>55</v>
       </c>
       <c r="T141">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U141" t="s">
         <v>55</v>
@@ -11177,22 +11168,22 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="B142">
-        <v>1015823</v>
+        <v>805465</v>
       </c>
       <c r="C142" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D142" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E142" t="s">
-        <v>407</v>
+        <v>98</v>
       </c>
       <c r="F142" s="6">
-        <v>15</v>
+        <v>15.38</v>
       </c>
       <c r="G142" s="7">
         <v>0</v>
@@ -11204,19 +11195,19 @@
         <v>80</v>
       </c>
       <c r="J142" s="6">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="K142" s="6">
-        <v>15</v>
+        <v>15.38</v>
       </c>
       <c r="L142" s="6">
-        <v>8.12</v>
+        <v>8.32</v>
       </c>
       <c r="M142" s="6">
-        <v>13.45</v>
+        <v>13.8</v>
       </c>
       <c r="N142" s="6">
-        <v>13.45</v>
+        <v>13.8</v>
       </c>
       <c r="O142" s="8">
         <v>-0.103</v>
@@ -11228,13 +11219,13 @@
         <v>57</v>
       </c>
       <c r="R142" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="S142" t="s">
         <v>55</v>
       </c>
       <c r="T142">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U142" t="s">
         <v>55</v>
@@ -11242,22 +11233,22 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="B143">
-        <v>805465</v>
+        <v>990715</v>
       </c>
       <c r="C143" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D143" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E143" t="s">
-        <v>98</v>
+        <v>270</v>
       </c>
       <c r="F143" s="6">
-        <v>15.38</v>
+        <v>9.23</v>
       </c>
       <c r="G143" s="7">
         <v>0</v>
@@ -11269,19 +11260,19 @@
         <v>80</v>
       </c>
       <c r="J143" s="6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K143" s="6">
-        <v>15.38</v>
+        <v>9.23</v>
       </c>
       <c r="L143" s="6">
-        <v>8.32</v>
+        <v>5</v>
       </c>
       <c r="M143" s="6">
-        <v>13.8</v>
+        <v>8.28</v>
       </c>
       <c r="N143" s="6">
-        <v>13.8</v>
+        <v>8.28</v>
       </c>
       <c r="O143" s="8">
         <v>-0.103</v>
@@ -11293,7 +11284,7 @@
         <v>57</v>
       </c>
       <c r="R143" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="S143" t="s">
         <v>55</v>
@@ -11307,22 +11298,22 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="B144">
-        <v>990715</v>
+        <v>881794</v>
       </c>
       <c r="C144" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D144" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E144" t="s">
-        <v>270</v>
+        <v>95</v>
       </c>
       <c r="F144" s="6">
-        <v>9.23</v>
+        <v>13.85</v>
       </c>
       <c r="G144" s="7">
         <v>0</v>
@@ -11334,19 +11325,19 @@
         <v>80</v>
       </c>
       <c r="J144" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K144" s="6">
-        <v>9.23</v>
+        <v>13.85</v>
       </c>
       <c r="L144" s="6">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="M144" s="6">
-        <v>8.28</v>
+        <v>12.42</v>
       </c>
       <c r="N144" s="6">
-        <v>8.28</v>
+        <v>12.42</v>
       </c>
       <c r="O144" s="8">
         <v>-0.103</v>
@@ -11372,22 +11363,22 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B145">
-        <v>881794</v>
+        <v>805466</v>
       </c>
       <c r="C145" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D145" t="s">
+        <v>410</v>
+      </c>
+      <c r="E145" t="s">
         <v>411</v>
       </c>
-      <c r="E145" t="s">
-        <v>95</v>
-      </c>
       <c r="F145" s="6">
-        <v>13.85</v>
+        <v>22.66</v>
       </c>
       <c r="G145" s="7">
         <v>0</v>
@@ -11399,19 +11390,19 @@
         <v>80</v>
       </c>
       <c r="J145" s="6">
-        <v>9</v>
+        <v>14.73</v>
       </c>
       <c r="K145" s="6">
-        <v>13.85</v>
+        <v>22.66</v>
       </c>
       <c r="L145" s="6">
-        <v>7.5</v>
+        <v>12.26</v>
       </c>
       <c r="M145" s="6">
-        <v>12.42</v>
+        <v>20.33</v>
       </c>
       <c r="N145" s="6">
-        <v>12.42</v>
+        <v>20.33</v>
       </c>
       <c r="O145" s="8">
         <v>-0.103</v>
@@ -11432,18 +11423,18 @@
         <v>0</v>
       </c>
       <c r="U145" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B146">
-        <v>805466</v>
+        <v>836358</v>
       </c>
       <c r="C146" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D146" t="s">
         <v>413</v>
@@ -11452,7 +11443,7 @@
         <v>414</v>
       </c>
       <c r="F146" s="6">
-        <v>22.66</v>
+        <v>19.23</v>
       </c>
       <c r="G146" s="7">
         <v>0</v>
@@ -11464,19 +11455,19 @@
         <v>80</v>
       </c>
       <c r="J146" s="6">
-        <v>14.73</v>
+        <v>12.5</v>
       </c>
       <c r="K146" s="6">
-        <v>22.66</v>
+        <v>19.23</v>
       </c>
       <c r="L146" s="6">
-        <v>12.26</v>
+        <v>10.41</v>
       </c>
       <c r="M146" s="6">
-        <v>20.33</v>
+        <v>17.25</v>
       </c>
       <c r="N146" s="6">
-        <v>20.33</v>
+        <v>17.25</v>
       </c>
       <c r="O146" s="8">
         <v>-0.103</v>
@@ -11502,13 +11493,13 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B147">
-        <v>836358</v>
+        <v>867239</v>
       </c>
       <c r="C147" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D147" t="s">
         <v>416</v>
@@ -11517,7 +11508,7 @@
         <v>417</v>
       </c>
       <c r="F147" s="6">
-        <v>19.23</v>
+        <v>20.77</v>
       </c>
       <c r="G147" s="7">
         <v>0</v>
@@ -11529,19 +11520,19 @@
         <v>80</v>
       </c>
       <c r="J147" s="6">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="K147" s="6">
-        <v>19.23</v>
+        <v>20.77</v>
       </c>
       <c r="L147" s="6">
-        <v>10.41</v>
+        <v>11.24</v>
       </c>
       <c r="M147" s="6">
-        <v>17.25</v>
+        <v>18.63</v>
       </c>
       <c r="N147" s="6">
-        <v>17.25</v>
+        <v>18.63</v>
       </c>
       <c r="O147" s="8">
         <v>-0.103</v>
@@ -11553,7 +11544,7 @@
         <v>57</v>
       </c>
       <c r="R147" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="S147" t="s">
         <v>55</v>
@@ -11567,22 +11558,22 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B148">
-        <v>867239</v>
+        <v>805468</v>
       </c>
       <c r="C148" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D148" t="s">
+        <v>418</v>
+      </c>
+      <c r="E148" t="s">
         <v>419</v>
       </c>
-      <c r="E148" t="s">
-        <v>420</v>
-      </c>
       <c r="F148" s="6">
-        <v>20.77</v>
+        <v>29.62</v>
       </c>
       <c r="G148" s="7">
         <v>0</v>
@@ -11594,19 +11585,19 @@
         <v>80</v>
       </c>
       <c r="J148" s="6">
-        <v>13.5</v>
+        <v>19.25</v>
       </c>
       <c r="K148" s="6">
-        <v>20.77</v>
+        <v>29.62</v>
       </c>
       <c r="L148" s="6">
-        <v>11.24</v>
+        <v>16.03</v>
       </c>
       <c r="M148" s="6">
-        <v>18.63</v>
+        <v>26.57</v>
       </c>
       <c r="N148" s="6">
-        <v>18.63</v>
+        <v>26.57</v>
       </c>
       <c r="O148" s="8">
         <v>-0.103</v>
@@ -11618,7 +11609,7 @@
         <v>57</v>
       </c>
       <c r="R148" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="S148" t="s">
         <v>55</v>
@@ -11632,13 +11623,13 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B149">
-        <v>805468</v>
+        <v>805469</v>
       </c>
       <c r="C149" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D149" t="s">
         <v>421</v>
@@ -11647,7 +11638,7 @@
         <v>422</v>
       </c>
       <c r="F149" s="6">
-        <v>29.62</v>
+        <v>32.69</v>
       </c>
       <c r="G149" s="7">
         <v>0</v>
@@ -11659,19 +11650,19 @@
         <v>80</v>
       </c>
       <c r="J149" s="6">
-        <v>19.25</v>
+        <v>21.25</v>
       </c>
       <c r="K149" s="6">
-        <v>29.62</v>
+        <v>32.69</v>
       </c>
       <c r="L149" s="6">
-        <v>16.03</v>
+        <v>17.69</v>
       </c>
       <c r="M149" s="6">
-        <v>26.57</v>
+        <v>29.32</v>
       </c>
       <c r="N149" s="6">
-        <v>26.57</v>
+        <v>29.32</v>
       </c>
       <c r="O149" s="8">
         <v>-0.103</v>
@@ -11697,13 +11688,13 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B150">
-        <v>805469</v>
+        <v>805461</v>
       </c>
       <c r="C150" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D150" t="s">
         <v>424</v>
@@ -11712,7 +11703,7 @@
         <v>425</v>
       </c>
       <c r="F150" s="6">
-        <v>32.69</v>
+        <v>23.08</v>
       </c>
       <c r="G150" s="7">
         <v>0</v>
@@ -11724,19 +11715,19 @@
         <v>80</v>
       </c>
       <c r="J150" s="6">
-        <v>21.25</v>
+        <v>15</v>
       </c>
       <c r="K150" s="6">
-        <v>32.69</v>
+        <v>23.08</v>
       </c>
       <c r="L150" s="6">
-        <v>17.69</v>
+        <v>12.49</v>
       </c>
       <c r="M150" s="6">
-        <v>29.32</v>
+        <v>20.7</v>
       </c>
       <c r="N150" s="6">
-        <v>29.32</v>
+        <v>20.7</v>
       </c>
       <c r="O150" s="8">
         <v>-0.103</v>
@@ -11757,18 +11748,18 @@
         <v>0</v>
       </c>
       <c r="U150" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B151">
-        <v>805461</v>
+        <v>805470</v>
       </c>
       <c r="C151" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D151" t="s">
         <v>427</v>
@@ -11777,7 +11768,7 @@
         <v>428</v>
       </c>
       <c r="F151" s="6">
-        <v>23.08</v>
+        <v>21.54</v>
       </c>
       <c r="G151" s="7">
         <v>0</v>
@@ -11789,19 +11780,19 @@
         <v>80</v>
       </c>
       <c r="J151" s="6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K151" s="6">
-        <v>23.08</v>
+        <v>21.54</v>
       </c>
       <c r="L151" s="6">
-        <v>12.49</v>
+        <v>11.66</v>
       </c>
       <c r="M151" s="6">
-        <v>20.7</v>
+        <v>19.32</v>
       </c>
       <c r="N151" s="6">
-        <v>20.7</v>
+        <v>19.32</v>
       </c>
       <c r="O151" s="8">
         <v>-0.103</v>
@@ -11827,22 +11818,22 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B152">
-        <v>805470</v>
+        <v>805471</v>
       </c>
       <c r="C152" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D152" t="s">
         <v>430</v>
       </c>
       <c r="E152" t="s">
-        <v>431</v>
+        <v>98</v>
       </c>
       <c r="F152" s="6">
-        <v>21.54</v>
+        <v>16.92</v>
       </c>
       <c r="G152" s="7">
         <v>0</v>
@@ -11854,19 +11845,19 @@
         <v>80</v>
       </c>
       <c r="J152" s="6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K152" s="6">
-        <v>21.54</v>
+        <v>16.92</v>
       </c>
       <c r="L152" s="6">
-        <v>11.66</v>
+        <v>9.16</v>
       </c>
       <c r="M152" s="6">
-        <v>19.32</v>
+        <v>15.18</v>
       </c>
       <c r="N152" s="6">
-        <v>19.32</v>
+        <v>15.18</v>
       </c>
       <c r="O152" s="8">
         <v>-0.103</v>
@@ -11878,7 +11869,7 @@
         <v>57</v>
       </c>
       <c r="R152" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="S152" t="s">
         <v>55</v>
@@ -11892,22 +11883,22 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B153">
-        <v>805471</v>
+        <v>805472</v>
       </c>
       <c r="C153" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D153" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E153" t="s">
-        <v>98</v>
+        <v>275</v>
       </c>
       <c r="F153" s="6">
-        <v>16.92</v>
+        <v>15.38</v>
       </c>
       <c r="G153" s="7">
         <v>0</v>
@@ -11919,19 +11910,19 @@
         <v>80</v>
       </c>
       <c r="J153" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K153" s="6">
-        <v>16.92</v>
+        <v>15.38</v>
       </c>
       <c r="L153" s="6">
-        <v>9.16</v>
+        <v>8.32</v>
       </c>
       <c r="M153" s="6">
-        <v>15.18</v>
+        <v>13.8</v>
       </c>
       <c r="N153" s="6">
-        <v>15.18</v>
+        <v>13.8</v>
       </c>
       <c r="O153" s="8">
         <v>-0.103</v>
@@ -11943,7 +11934,7 @@
         <v>57</v>
       </c>
       <c r="R153" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="S153" t="s">
         <v>55</v>
@@ -11957,19 +11948,19 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B154">
-        <v>805472</v>
+        <v>805473</v>
       </c>
       <c r="C154" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D154" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E154" t="s">
-        <v>275</v>
+        <v>95</v>
       </c>
       <c r="F154" s="6">
         <v>15.38</v>
@@ -12008,7 +11999,7 @@
         <v>57</v>
       </c>
       <c r="R154" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="S154" t="s">
         <v>55</v>
@@ -12022,19 +12013,19 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B155">
-        <v>805473</v>
+        <v>805474</v>
       </c>
       <c r="C155" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D155" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E155" t="s">
-        <v>95</v>
+        <v>425</v>
       </c>
       <c r="F155" s="6">
         <v>15.38</v>
@@ -12073,7 +12064,7 @@
         <v>57</v>
       </c>
       <c r="R155" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="S155" t="s">
         <v>55</v>
@@ -12087,22 +12078,22 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B156">
-        <v>805474</v>
+        <v>990712</v>
       </c>
       <c r="C156" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D156" t="s">
+        <v>438</v>
+      </c>
+      <c r="E156" t="s">
         <v>439</v>
       </c>
-      <c r="E156" t="s">
-        <v>428</v>
-      </c>
       <c r="F156" s="6">
-        <v>15.38</v>
+        <v>8.92</v>
       </c>
       <c r="G156" s="7">
         <v>0</v>
@@ -12114,19 +12105,19 @@
         <v>80</v>
       </c>
       <c r="J156" s="6">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="K156" s="6">
-        <v>15.38</v>
+        <v>8.92</v>
       </c>
       <c r="L156" s="6">
-        <v>8.32</v>
+        <v>4.83</v>
       </c>
       <c r="M156" s="6">
-        <v>13.8</v>
+        <v>8</v>
       </c>
       <c r="N156" s="6">
-        <v>13.8</v>
+        <v>8</v>
       </c>
       <c r="O156" s="8">
         <v>-0.103</v>
@@ -12138,7 +12129,7 @@
         <v>57</v>
       </c>
       <c r="R156" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="S156" t="s">
         <v>55</v>
@@ -12152,22 +12143,22 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B157">
-        <v>990712</v>
+        <v>805475</v>
       </c>
       <c r="C157" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D157" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E157" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="F157" s="6">
-        <v>8.92</v>
+        <v>18.46</v>
       </c>
       <c r="G157" s="7">
         <v>0</v>
@@ -12179,19 +12170,19 @@
         <v>80</v>
       </c>
       <c r="J157" s="6">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="K157" s="6">
-        <v>8.92</v>
+        <v>18.46</v>
       </c>
       <c r="L157" s="6">
-        <v>4.83</v>
+        <v>9.99</v>
       </c>
       <c r="M157" s="6">
-        <v>8</v>
+        <v>16.56</v>
       </c>
       <c r="N157" s="6">
-        <v>8</v>
+        <v>16.56</v>
       </c>
       <c r="O157" s="8">
         <v>-0.103</v>
@@ -12203,7 +12194,7 @@
         <v>57</v>
       </c>
       <c r="R157" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="S157" t="s">
         <v>55</v>
@@ -12217,22 +12208,22 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B158">
-        <v>805475</v>
+        <v>805476</v>
       </c>
       <c r="C158" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D158" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E158" t="s">
-        <v>431</v>
+        <v>98</v>
       </c>
       <c r="F158" s="6">
-        <v>18.46</v>
+        <v>10.77</v>
       </c>
       <c r="G158" s="7">
         <v>0</v>
@@ -12244,19 +12235,19 @@
         <v>80</v>
       </c>
       <c r="J158" s="6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K158" s="6">
-        <v>18.46</v>
+        <v>10.77</v>
       </c>
       <c r="L158" s="6">
-        <v>9.99</v>
+        <v>5.83</v>
       </c>
       <c r="M158" s="6">
-        <v>16.56</v>
+        <v>9.66</v>
       </c>
       <c r="N158" s="6">
-        <v>16.56</v>
+        <v>9.66</v>
       </c>
       <c r="O158" s="8">
         <v>-0.103</v>
@@ -12268,7 +12259,7 @@
         <v>57</v>
       </c>
       <c r="R158" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="S158" t="s">
         <v>55</v>
@@ -12282,22 +12273,22 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B159">
-        <v>805476</v>
+        <v>805477</v>
       </c>
       <c r="C159" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D159" t="s">
+        <v>444</v>
+      </c>
+      <c r="E159" t="s">
         <v>445</v>
       </c>
-      <c r="E159" t="s">
-        <v>98</v>
-      </c>
       <c r="F159" s="6">
-        <v>10.77</v>
+        <v>18.46</v>
       </c>
       <c r="G159" s="7">
         <v>0</v>
@@ -12309,19 +12300,19 @@
         <v>80</v>
       </c>
       <c r="J159" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K159" s="6">
-        <v>10.77</v>
+        <v>18.46</v>
       </c>
       <c r="L159" s="6">
-        <v>5.83</v>
+        <v>9.99</v>
       </c>
       <c r="M159" s="6">
-        <v>9.66</v>
+        <v>16.56</v>
       </c>
       <c r="N159" s="6">
-        <v>9.66</v>
+        <v>16.56</v>
       </c>
       <c r="O159" s="8">
         <v>-0.103</v>
@@ -12342,71 +12333,6 @@
         <v>0</v>
       </c>
       <c r="U159" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A160">
-        <v>163</v>
-      </c>
-      <c r="B160">
-        <v>805477</v>
-      </c>
-      <c r="C160" t="s">
-        <v>378</v>
-      </c>
-      <c r="D160" t="s">
-        <v>447</v>
-      </c>
-      <c r="E160" t="s">
-        <v>448</v>
-      </c>
-      <c r="F160" s="6">
-        <v>18.46</v>
-      </c>
-      <c r="G160" s="7">
-        <v>0</v>
-      </c>
-      <c r="H160" s="7">
-        <v>0</v>
-      </c>
-      <c r="I160" t="s">
-        <v>80</v>
-      </c>
-      <c r="J160" s="6">
-        <v>12</v>
-      </c>
-      <c r="K160" s="6">
-        <v>18.46</v>
-      </c>
-      <c r="L160" s="6">
-        <v>9.99</v>
-      </c>
-      <c r="M160" s="6">
-        <v>16.56</v>
-      </c>
-      <c r="N160" s="6">
-        <v>16.56</v>
-      </c>
-      <c r="O160" s="8">
-        <v>-0.103</v>
-      </c>
-      <c r="P160">
-        <v>1</v>
-      </c>
-      <c r="Q160" t="s">
-        <v>57</v>
-      </c>
-      <c r="R160" t="s">
-        <v>449</v>
-      </c>
-      <c r="S160" t="s">
-        <v>55</v>
-      </c>
-      <c r="T160">
-        <v>0</v>
-      </c>
-      <c r="U160" t="s">
         <v>55</v>
       </c>
     </row>
@@ -12423,10 +12349,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -12434,7 +12360,7 @@
         <v>0.5412</v>
       </c>
       <c r="B2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -12442,7 +12368,7 @@
         <v>0.65</v>
       </c>
       <c r="B3" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -12450,7 +12376,7 @@
         <v>0.6574</v>
       </c>
       <c r="B4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -12458,7 +12384,7 @@
         <v>0.6574</v>
       </c>
       <c r="B5" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="454">
   <si>
     <t>Master Pricelist - Deck Family Farm</t>
   </si>
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-20T14:10:14.634Z</t>
+    <t>2026-03-21T11:16:02.010Z</t>
   </si>
   <si>
     <t>Environment</t>
@@ -284,7 +284,7 @@
     <t>Smoked Pork Hocks -Skin-on and Smoked</t>
   </si>
   <si>
-    <t>2 - 2.5 lbs</t>
+    <t>0.8 - 1.2 lbs</t>
   </si>
   <si>
     <t xml:space="preserve"> A flavorful favorite for soups, stews, greens, and beans. These savory, smoky hocks infuse dishes with rich, deep flavor and natural gelatin, adding heartiness to every bite.
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>Smoked Pork Shanks - Skin-on and Smoked</t>
+  </si>
+  <si>
+    <t>2 - 2.5 lbs</t>
   </si>
   <si>
     <t xml:space="preserve">Boasting more meat than the hocks, these savory, smoky shanks infuse dishes with rich, deep flavor and ample amounts of shredded meat.
@@ -2866,10 +2869,10 @@
         <v>16.5</v>
       </c>
       <c r="G14" s="7">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="H14" s="7">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="I14" t="s">
         <v>80</v>
@@ -2925,7 +2928,7 @@
         <v>91</v>
       </c>
       <c r="E15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F15" s="6">
         <v>16.5</v>
@@ -2964,7 +2967,7 @@
         <v>55</v>
       </c>
       <c r="R15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="S15" t="s">
         <v>57</v>
@@ -2984,13 +2987,13 @@
         <v>806161</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F16" s="6">
         <v>26</v>
@@ -3029,7 +3032,7 @@
         <v>55</v>
       </c>
       <c r="R16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="S16" t="s">
         <v>57</v>
@@ -3049,13 +3052,13 @@
         <v>941000</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F17" s="6">
         <v>47.5</v>
@@ -3094,7 +3097,7 @@
         <v>55</v>
       </c>
       <c r="R17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="S17" t="s">
         <v>57</v>
@@ -3114,13 +3117,13 @@
         <v>940998</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F18" s="6">
         <v>17</v>
@@ -3159,7 +3162,7 @@
         <v>55</v>
       </c>
       <c r="R18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="S18" t="s">
         <v>57</v>
@@ -3179,13 +3182,13 @@
         <v>806159</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F19" s="6">
         <v>25</v>
@@ -3224,7 +3227,7 @@
         <v>55</v>
       </c>
       <c r="R19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S19" t="s">
         <v>57</v>
@@ -3244,13 +3247,13 @@
         <v>940994</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F20" s="6">
         <v>14</v>
@@ -3289,7 +3292,7 @@
         <v>55</v>
       </c>
       <c r="R20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S20" t="s">
         <v>57</v>
@@ -3309,13 +3312,13 @@
         <v>960228</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F21" s="6">
         <v>26</v>
@@ -3354,16 +3357,16 @@
         <v>55</v>
       </c>
       <c r="R21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="S21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -3374,10 +3377,10 @@
         <v>813072</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E22" t="s">
         <v>83</v>
@@ -3419,7 +3422,7 @@
         <v>55</v>
       </c>
       <c r="R22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S22" t="s">
         <v>55</v>
@@ -3439,10 +3442,10 @@
         <v>922135</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E23" t="s">
         <v>64</v>
@@ -3484,7 +3487,7 @@
         <v>55</v>
       </c>
       <c r="R23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S23" t="s">
         <v>57</v>
@@ -3504,13 +3507,13 @@
         <v>813075</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F24" s="6">
         <v>26</v>
@@ -3549,7 +3552,7 @@
         <v>55</v>
       </c>
       <c r="R24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S24" t="s">
         <v>57</v>
@@ -3569,13 +3572,13 @@
         <v>805660</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F25" s="6">
         <v>9.5</v>
@@ -3614,13 +3617,13 @@
         <v>55</v>
       </c>
       <c r="R25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="S25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="s">
         <v>55</v>
@@ -3634,13 +3637,13 @@
         <v>825832</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F26" s="6">
         <v>26</v>
@@ -3679,7 +3682,7 @@
         <v>55</v>
       </c>
       <c r="R26" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="S26" t="s">
         <v>57</v>
@@ -3699,13 +3702,13 @@
         <v>841579</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E27" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F27" s="6">
         <v>26</v>
@@ -3744,7 +3747,7 @@
         <v>55</v>
       </c>
       <c r="R27" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="S27" t="s">
         <v>57</v>
@@ -3764,10 +3767,10 @@
         <v>825834</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E28" t="s">
         <v>64</v>
@@ -3809,7 +3812,7 @@
         <v>55</v>
       </c>
       <c r="R28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S28" t="s">
         <v>57</v>
@@ -3829,13 +3832,13 @@
         <v>813076</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F29" s="6">
         <v>13</v>
@@ -3874,16 +3877,16 @@
         <v>55</v>
       </c>
       <c r="R29" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="S29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3894,13 +3897,13 @@
         <v>813071</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E30" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F30" s="6">
         <v>19.5</v>
@@ -3939,7 +3942,7 @@
         <v>55</v>
       </c>
       <c r="R30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="S30" t="s">
         <v>57</v>
@@ -3959,13 +3962,13 @@
         <v>894281</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F31" s="6">
         <v>19.5</v>
@@ -4004,7 +4007,7 @@
         <v>55</v>
       </c>
       <c r="R31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="S31" t="s">
         <v>57</v>
@@ -4024,10 +4027,10 @@
         <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E32" t="s">
         <v>80</v>
@@ -4089,13 +4092,13 @@
         <v>805667</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F33" s="6">
         <v>18.5</v>
@@ -4134,7 +4137,7 @@
         <v>55</v>
       </c>
       <c r="R33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="S33" t="s">
         <v>57</v>
@@ -4154,13 +4157,13 @@
         <v>813067</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D34" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F34" s="6">
         <v>43</v>
@@ -4199,16 +4202,16 @@
         <v>55</v>
       </c>
       <c r="R34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S34" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="U34" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -4219,13 +4222,13 @@
         <v>825833</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F35" s="6">
         <v>9.5</v>
@@ -4264,13 +4267,13 @@
         <v>55</v>
       </c>
       <c r="R35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="S35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U35" t="s">
         <v>55</v>
@@ -4284,13 +4287,13 @@
         <v>869027</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D36" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E36" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F36" s="6">
         <v>21</v>
@@ -4329,16 +4332,16 @@
         <v>55</v>
       </c>
       <c r="R36" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="S36" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U36" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -4349,13 +4352,13 @@
         <v>856878</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D37" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E37" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F37" s="6">
         <v>16</v>
@@ -4394,13 +4397,13 @@
         <v>55</v>
       </c>
       <c r="R37" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="S37" t="s">
         <v>55</v>
       </c>
       <c r="T37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U37" t="s">
         <v>55</v>
@@ -4414,13 +4417,13 @@
         <v>941001</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D38" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F38" s="6">
         <v>17</v>
@@ -4459,7 +4462,7 @@
         <v>55</v>
       </c>
       <c r="R38" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="S38" t="s">
         <v>55</v>
@@ -4479,13 +4482,13 @@
         <v>941002</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D39" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E39" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F39" s="6">
         <v>18</v>
@@ -4524,7 +4527,7 @@
         <v>55</v>
       </c>
       <c r="R39" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="S39" t="s">
         <v>57</v>
@@ -4544,13 +4547,13 @@
         <v>805658</v>
       </c>
       <c r="C40" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F40" s="6">
         <v>16</v>
@@ -4589,7 +4592,7 @@
         <v>55</v>
       </c>
       <c r="R40" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="S40" t="s">
         <v>57</v>
@@ -4609,13 +4612,13 @@
         <v>813074</v>
       </c>
       <c r="C41" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D41" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E41" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F41" s="6">
         <v>26</v>
@@ -4654,16 +4657,16 @@
         <v>55</v>
       </c>
       <c r="R41" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S41" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U41" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -4674,10 +4677,10 @@
         <v>805664</v>
       </c>
       <c r="C42" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D42" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E42" t="s">
         <v>59</v>
@@ -4719,7 +4722,7 @@
         <v>55</v>
       </c>
       <c r="R42" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S42" t="s">
         <v>57</v>
@@ -4739,13 +4742,13 @@
         <v>825830</v>
       </c>
       <c r="C43" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D43" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E43" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F43" s="6">
         <v>26</v>
@@ -4784,7 +4787,7 @@
         <v>55</v>
       </c>
       <c r="R43" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S43" t="s">
         <v>55</v>
@@ -4804,13 +4807,13 @@
         <v>805701</v>
       </c>
       <c r="C44" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D44" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E44" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F44" s="6">
         <v>19.5</v>
@@ -4849,7 +4852,7 @@
         <v>55</v>
       </c>
       <c r="R44" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="S44" t="s">
         <v>57</v>
@@ -4869,13 +4872,13 @@
         <v>805688</v>
       </c>
       <c r="C45" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D45" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E45" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F45" s="6">
         <v>12</v>
@@ -4914,7 +4917,7 @@
         <v>55</v>
       </c>
       <c r="R45" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="S45" t="s">
         <v>57</v>
@@ -4934,13 +4937,13 @@
         <v>805716</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D46" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F46" s="6">
         <v>37</v>
@@ -4979,7 +4982,7 @@
         <v>55</v>
       </c>
       <c r="R46" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="S46" t="s">
         <v>57</v>
@@ -4999,13 +5002,13 @@
         <v>805689</v>
       </c>
       <c r="C47" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D47" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E47" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="6">
         <v>12</v>
@@ -5044,7 +5047,7 @@
         <v>55</v>
       </c>
       <c r="R47" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S47" t="s">
         <v>57</v>
@@ -5064,13 +5067,13 @@
         <v>805668</v>
       </c>
       <c r="C48" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D48" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E48" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F48" s="6">
         <v>40.5</v>
@@ -5109,7 +5112,7 @@
         <v>55</v>
       </c>
       <c r="R48" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="S48" t="s">
         <v>57</v>
@@ -5129,13 +5132,13 @@
         <v>929452</v>
       </c>
       <c r="C49" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D49" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E49" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F49" s="6">
         <v>26</v>
@@ -5174,16 +5177,16 @@
         <v>55</v>
       </c>
       <c r="R49" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="S49" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U49" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -5194,13 +5197,13 @@
         <v>894282</v>
       </c>
       <c r="C50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E50" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6">
         <v>26</v>
@@ -5239,16 +5242,16 @@
         <v>55</v>
       </c>
       <c r="R50" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="S50" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U50" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -5259,13 +5262,13 @@
         <v>813069</v>
       </c>
       <c r="C51" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D51" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E51" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F51" s="6">
         <v>26</v>
@@ -5304,16 +5307,16 @@
         <v>55</v>
       </c>
       <c r="R51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="S51" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U51" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -5324,13 +5327,13 @@
         <v>814845</v>
       </c>
       <c r="C52" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D52" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E52" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6">
         <v>25</v>
@@ -5369,7 +5372,7 @@
         <v>55</v>
       </c>
       <c r="R52" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="S52" t="s">
         <v>57</v>
@@ -5389,13 +5392,13 @@
         <v>883799</v>
       </c>
       <c r="C53" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D53" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E53" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F53" s="6">
         <v>5</v>
@@ -5434,7 +5437,7 @@
         <v>55</v>
       </c>
       <c r="R53" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="S53" t="s">
         <v>55</v>
@@ -5454,13 +5457,13 @@
         <v>813079</v>
       </c>
       <c r="C54" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D54" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E54" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F54" s="6">
         <v>9.5</v>
@@ -5499,7 +5502,7 @@
         <v>55</v>
       </c>
       <c r="R54" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="S54" t="s">
         <v>57</v>
@@ -5519,13 +5522,13 @@
         <v>818957</v>
       </c>
       <c r="C55" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D55" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F55" s="6">
         <v>9.5</v>
@@ -5564,7 +5567,7 @@
         <v>55</v>
       </c>
       <c r="R55" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="S55" t="s">
         <v>57</v>
@@ -5584,13 +5587,13 @@
         <v>805677</v>
       </c>
       <c r="C56" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D56" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E56" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F56" s="6">
         <v>12</v>
@@ -5629,7 +5632,7 @@
         <v>55</v>
       </c>
       <c r="R56" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S56" t="s">
         <v>57</v>
@@ -5649,13 +5652,13 @@
         <v>805669</v>
       </c>
       <c r="C57" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D57" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E57" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F57" s="6">
         <v>14</v>
@@ -5694,7 +5697,7 @@
         <v>55</v>
       </c>
       <c r="R57" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="S57" t="s">
         <v>57</v>
@@ -5714,13 +5717,13 @@
         <v>805676</v>
       </c>
       <c r="C58" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D58" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E58" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F58" s="6">
         <v>12</v>
@@ -5759,7 +5762,7 @@
         <v>55</v>
       </c>
       <c r="R58" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="S58" t="s">
         <v>57</v>
@@ -5779,13 +5782,13 @@
         <v>805679</v>
       </c>
       <c r="C59" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D59" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E59" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F59" s="6">
         <v>12</v>
@@ -5824,7 +5827,7 @@
         <v>55</v>
       </c>
       <c r="R59" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="S59" t="s">
         <v>57</v>
@@ -5844,13 +5847,13 @@
         <v>805673</v>
       </c>
       <c r="C60" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D60" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E60" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F60" s="6">
         <v>9</v>
@@ -5889,7 +5892,7 @@
         <v>55</v>
       </c>
       <c r="R60" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="S60" t="s">
         <v>57</v>
@@ -5909,13 +5912,13 @@
         <v>953035</v>
       </c>
       <c r="C61" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D61" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E61" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F61" s="6">
         <v>9.5</v>
@@ -5954,7 +5957,7 @@
         <v>55</v>
       </c>
       <c r="R61" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="S61" t="s">
         <v>57</v>
@@ -5974,13 +5977,13 @@
         <v>953036</v>
       </c>
       <c r="C62" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D62" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E62" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F62" s="6">
         <v>10</v>
@@ -6019,7 +6022,7 @@
         <v>55</v>
       </c>
       <c r="R62" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="S62" t="s">
         <v>57</v>
@@ -6039,13 +6042,13 @@
         <v>953039</v>
       </c>
       <c r="C63" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D63" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E63" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F63" s="6">
         <v>10.5</v>
@@ -6084,7 +6087,7 @@
         <v>55</v>
       </c>
       <c r="R63" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="S63" t="s">
         <v>57</v>
@@ -6104,13 +6107,13 @@
         <v>1004600</v>
       </c>
       <c r="C64" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D64" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E64" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F64" s="6">
         <v>12</v>
@@ -6149,7 +6152,7 @@
         <v>55</v>
       </c>
       <c r="R64" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="S64" t="s">
         <v>57</v>
@@ -6169,13 +6172,13 @@
         <v>1004599</v>
       </c>
       <c r="C65" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D65" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E65" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F65" s="6">
         <v>12</v>
@@ -6214,7 +6217,7 @@
         <v>55</v>
       </c>
       <c r="R65" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="S65" t="s">
         <v>57</v>
@@ -6234,13 +6237,13 @@
         <v>805661</v>
       </c>
       <c r="C66" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D66" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E66" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F66" s="6">
         <v>12</v>
@@ -6279,7 +6282,7 @@
         <v>55</v>
       </c>
       <c r="R66" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="S66" t="s">
         <v>57</v>
@@ -6299,13 +6302,13 @@
         <v>805685</v>
       </c>
       <c r="C67" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D67" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E67" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F67" s="6">
         <v>18.5</v>
@@ -6344,7 +6347,7 @@
         <v>55</v>
       </c>
       <c r="R67" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="S67" t="s">
         <v>57</v>
@@ -6364,13 +6367,13 @@
         <v>814849</v>
       </c>
       <c r="C68" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D68" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E68" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F68" s="6">
         <v>12</v>
@@ -6409,7 +6412,7 @@
         <v>55</v>
       </c>
       <c r="R68" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="S68" t="s">
         <v>57</v>
@@ -6429,10 +6432,10 @@
         <v>813092</v>
       </c>
       <c r="C69" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D69" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E69" t="s">
         <v>59</v>
@@ -6474,7 +6477,7 @@
         <v>55</v>
       </c>
       <c r="R69" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="S69" t="s">
         <v>57</v>
@@ -6494,10 +6497,10 @@
         <v>825835</v>
       </c>
       <c r="C70" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D70" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E70" t="s">
         <v>64</v>
@@ -6539,7 +6542,7 @@
         <v>55</v>
       </c>
       <c r="R70" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="S70" t="s">
         <v>57</v>
@@ -6559,13 +6562,13 @@
         <v>922133</v>
       </c>
       <c r="C71" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D71" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E71" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F71" s="6">
         <v>24</v>
@@ -6604,7 +6607,7 @@
         <v>55</v>
       </c>
       <c r="R71" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="S71" t="s">
         <v>57</v>
@@ -6624,13 +6627,13 @@
         <v>913064</v>
       </c>
       <c r="C72" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D72" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E72" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F72" s="6">
         <v>24</v>
@@ -6669,7 +6672,7 @@
         <v>55</v>
       </c>
       <c r="R72" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="S72" t="s">
         <v>57</v>
@@ -6689,13 +6692,13 @@
         <v>939774</v>
       </c>
       <c r="C73" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D73" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E73" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F73" s="6">
         <v>9.5</v>
@@ -6734,7 +6737,7 @@
         <v>55</v>
       </c>
       <c r="R73" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S73" t="s">
         <v>55</v>
@@ -6754,13 +6757,13 @@
         <v>825839</v>
       </c>
       <c r="C74" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D74" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E74" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F74" s="6">
         <v>21.5</v>
@@ -6799,7 +6802,7 @@
         <v>55</v>
       </c>
       <c r="R74" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="S74" t="s">
         <v>57</v>
@@ -6819,13 +6822,13 @@
         <v>805703</v>
       </c>
       <c r="C75" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D75" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E75" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F75" s="6">
         <v>15.5</v>
@@ -6864,7 +6867,7 @@
         <v>55</v>
       </c>
       <c r="R75" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="S75" t="s">
         <v>57</v>
@@ -6884,13 +6887,13 @@
         <v>825840</v>
       </c>
       <c r="C76" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D76" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E76" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F76" s="6">
         <v>16</v>
@@ -6929,7 +6932,7 @@
         <v>55</v>
       </c>
       <c r="R76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="S76" t="s">
         <v>57</v>
@@ -6949,13 +6952,13 @@
         <v>805710</v>
       </c>
       <c r="C77" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D77" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E77" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F77" s="6">
         <v>16</v>
@@ -6994,7 +6997,7 @@
         <v>55</v>
       </c>
       <c r="R77" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="S77" t="s">
         <v>57</v>
@@ -7014,13 +7017,13 @@
         <v>805711</v>
       </c>
       <c r="C78" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D78" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F78" s="6">
         <v>20</v>
@@ -7059,7 +7062,7 @@
         <v>55</v>
       </c>
       <c r="R78" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="S78" t="s">
         <v>57</v>
@@ -7079,10 +7082,10 @@
         <v>78</v>
       </c>
       <c r="C79" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D79" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E79" t="s">
         <v>80</v>
@@ -7144,13 +7147,13 @@
         <v>805712</v>
       </c>
       <c r="C80" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D80" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E80" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F80" s="6">
         <v>21.5</v>
@@ -7189,7 +7192,7 @@
         <v>55</v>
       </c>
       <c r="R80" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="S80" t="s">
         <v>57</v>
@@ -7209,13 +7212,13 @@
         <v>805659</v>
       </c>
       <c r="C81" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D81" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E81" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F81" s="6">
         <v>21.5</v>
@@ -7254,7 +7257,7 @@
         <v>55</v>
       </c>
       <c r="R81" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="S81" t="s">
         <v>55</v>
@@ -7274,13 +7277,13 @@
         <v>805653</v>
       </c>
       <c r="C82" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D82" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E82" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F82" s="6">
         <v>14.5</v>
@@ -7319,7 +7322,7 @@
         <v>55</v>
       </c>
       <c r="R82" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="S82" t="s">
         <v>57</v>
@@ -7339,13 +7342,13 @@
         <v>805724</v>
       </c>
       <c r="C83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D83" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E83" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F83" s="6">
         <v>13.2</v>
@@ -7384,7 +7387,7 @@
         <v>55</v>
       </c>
       <c r="R83" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="S83" t="s">
         <v>57</v>
@@ -7404,13 +7407,13 @@
         <v>813084</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D84" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E84" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F84" s="6">
         <v>19.5</v>
@@ -7449,7 +7452,7 @@
         <v>55</v>
       </c>
       <c r="R84" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="S84" t="s">
         <v>57</v>
@@ -7469,13 +7472,13 @@
         <v>813086</v>
       </c>
       <c r="C85" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D85" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E85" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F85" s="6">
         <v>15.5</v>
@@ -7514,7 +7517,7 @@
         <v>55</v>
       </c>
       <c r="R85" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="S85" t="s">
         <v>57</v>
@@ -7534,13 +7537,13 @@
         <v>805686</v>
       </c>
       <c r="C86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D86" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E86" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F86" s="6">
         <v>19.5</v>
@@ -7579,7 +7582,7 @@
         <v>55</v>
       </c>
       <c r="R86" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="S86" t="s">
         <v>57</v>
@@ -7599,13 +7602,13 @@
         <v>805693</v>
       </c>
       <c r="C87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D87" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E87" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F87" s="6">
         <v>19.5</v>
@@ -7644,7 +7647,7 @@
         <v>55</v>
       </c>
       <c r="R87" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="S87" t="s">
         <v>57</v>
@@ -7664,13 +7667,13 @@
         <v>882704</v>
       </c>
       <c r="C88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D88" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E88" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F88" s="6">
         <v>21.5</v>
@@ -7709,7 +7712,7 @@
         <v>55</v>
       </c>
       <c r="R88" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="S88" t="s">
         <v>57</v>
@@ -7729,13 +7732,13 @@
         <v>963826</v>
       </c>
       <c r="C89" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D89" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E89" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F89" s="6">
         <v>21.5</v>
@@ -7774,7 +7777,7 @@
         <v>55</v>
       </c>
       <c r="R89" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="S89" t="s">
         <v>57</v>
@@ -7794,13 +7797,13 @@
         <v>805713</v>
       </c>
       <c r="C90" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D90" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E90" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F90" s="6">
         <v>16.5</v>
@@ -7839,7 +7842,7 @@
         <v>55</v>
       </c>
       <c r="R90" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="S90" t="s">
         <v>57</v>
@@ -7859,13 +7862,13 @@
         <v>827440</v>
       </c>
       <c r="C91" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D91" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E91" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F91" s="6">
         <v>20</v>
@@ -7904,7 +7907,7 @@
         <v>55</v>
       </c>
       <c r="R91" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="S91" t="s">
         <v>57</v>
@@ -7924,13 +7927,13 @@
         <v>901753</v>
       </c>
       <c r="C92" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D92" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E92" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F92" s="6">
         <v>21.5</v>
@@ -7969,7 +7972,7 @@
         <v>55</v>
       </c>
       <c r="R92" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="S92" t="s">
         <v>57</v>
@@ -7989,13 +7992,13 @@
         <v>859028</v>
       </c>
       <c r="C93" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D93" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E93" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F93" s="6">
         <v>18</v>
@@ -8034,7 +8037,7 @@
         <v>55</v>
       </c>
       <c r="R93" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="S93" t="s">
         <v>57</v>
@@ -8054,13 +8057,13 @@
         <v>805675</v>
       </c>
       <c r="C94" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D94" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E94" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F94" s="6">
         <v>18</v>
@@ -8099,7 +8102,7 @@
         <v>55</v>
       </c>
       <c r="R94" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="S94" t="s">
         <v>57</v>
@@ -8119,13 +8122,13 @@
         <v>805719</v>
       </c>
       <c r="C95" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D95" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E95" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F95" s="6">
         <v>20</v>
@@ -8164,7 +8167,7 @@
         <v>55</v>
       </c>
       <c r="R95" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="S95" t="s">
         <v>57</v>
@@ -8184,13 +8187,13 @@
         <v>805720</v>
       </c>
       <c r="C96" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D96" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E96" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F96" s="6">
         <v>18</v>
@@ -8229,7 +8232,7 @@
         <v>55</v>
       </c>
       <c r="R96" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="S96" t="s">
         <v>57</v>
@@ -8249,13 +8252,13 @@
         <v>805721</v>
       </c>
       <c r="C97" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D97" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E97" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F97" s="6">
         <v>15</v>
@@ -8294,7 +8297,7 @@
         <v>55</v>
       </c>
       <c r="R97" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="S97" t="s">
         <v>57</v>
@@ -8314,13 +8317,13 @@
         <v>805682</v>
       </c>
       <c r="C98" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D98" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E98" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F98" s="6">
         <v>19.5</v>
@@ -8359,7 +8362,7 @@
         <v>55</v>
       </c>
       <c r="R98" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="S98" t="s">
         <v>57</v>
@@ -8379,13 +8382,13 @@
         <v>805670</v>
       </c>
       <c r="C99" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D99" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E99" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F99" s="6">
         <v>20</v>
@@ -8424,7 +8427,7 @@
         <v>55</v>
       </c>
       <c r="R99" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="S99" t="s">
         <v>57</v>
@@ -8444,13 +8447,13 @@
         <v>805678</v>
       </c>
       <c r="C100" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D100" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E100" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F100" s="6">
         <v>16.5</v>
@@ -8489,7 +8492,7 @@
         <v>55</v>
       </c>
       <c r="R100" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="S100" t="s">
         <v>57</v>
@@ -8509,13 +8512,13 @@
         <v>940154</v>
       </c>
       <c r="C101" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D101" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E101" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F101" s="6">
         <v>11</v>
@@ -8554,7 +8557,7 @@
         <v>55</v>
       </c>
       <c r="R101" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="S101" t="s">
         <v>57</v>
@@ -8574,13 +8577,13 @@
         <v>805687</v>
       </c>
       <c r="C102" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D102" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E102" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F102" s="6">
         <v>17</v>
@@ -8619,7 +8622,7 @@
         <v>55</v>
       </c>
       <c r="R102" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="S102" t="s">
         <v>57</v>
@@ -8639,13 +8642,13 @@
         <v>805692</v>
       </c>
       <c r="C103" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D103" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E103" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F103" s="6">
         <v>19.5</v>
@@ -8684,7 +8687,7 @@
         <v>55</v>
       </c>
       <c r="R103" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="S103" t="s">
         <v>57</v>
@@ -8704,13 +8707,13 @@
         <v>805694</v>
       </c>
       <c r="C104" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D104" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E104" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F104" s="6">
         <v>18</v>
@@ -8749,7 +8752,7 @@
         <v>55</v>
       </c>
       <c r="R104" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="S104" t="s">
         <v>57</v>
@@ -8769,13 +8772,13 @@
         <v>941005</v>
       </c>
       <c r="C105" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D105" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F105" s="6">
         <v>12</v>
@@ -8814,7 +8817,7 @@
         <v>55</v>
       </c>
       <c r="R105" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="S105" t="s">
         <v>57</v>
@@ -8834,13 +8837,13 @@
         <v>805459</v>
       </c>
       <c r="C106" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D106" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E106" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F106" s="6">
         <v>7</v>
@@ -8879,7 +8882,7 @@
         <v>55</v>
       </c>
       <c r="R106" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="S106" t="s">
         <v>57</v>
@@ -8899,13 +8902,13 @@
         <v>995135</v>
       </c>
       <c r="C107" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D107" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E107" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F107" s="6">
         <v>10</v>
@@ -8944,7 +8947,7 @@
         <v>55</v>
       </c>
       <c r="R107" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="S107" t="s">
         <v>55</v>
@@ -8964,13 +8967,13 @@
         <v>900311</v>
       </c>
       <c r="C108" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D108" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E108" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F108" s="6">
         <v>20</v>
@@ -9009,7 +9012,7 @@
         <v>55</v>
       </c>
       <c r="R108" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="S108" t="s">
         <v>57</v>
@@ -9029,13 +9032,13 @@
         <v>840823</v>
       </c>
       <c r="C109" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D109" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E109" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F109" s="6">
         <v>16.5</v>
@@ -9074,7 +9077,7 @@
         <v>55</v>
       </c>
       <c r="R109" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="S109" t="s">
         <v>57</v>
@@ -9094,13 +9097,13 @@
         <v>913652</v>
       </c>
       <c r="C110" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D110" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E110" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F110" s="6">
         <v>16.5</v>
@@ -9139,7 +9142,7 @@
         <v>55</v>
       </c>
       <c r="R110" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="S110" t="s">
         <v>57</v>
@@ -9159,13 +9162,13 @@
         <v>913651</v>
       </c>
       <c r="C111" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D111" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E111" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F111" s="6">
         <v>16.5</v>
@@ -9204,7 +9207,7 @@
         <v>55</v>
       </c>
       <c r="R111" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="S111" t="s">
         <v>57</v>
@@ -9224,13 +9227,13 @@
         <v>816905</v>
       </c>
       <c r="C112" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D112" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E112" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F112" s="6">
         <v>20</v>
@@ -9269,7 +9272,7 @@
         <v>55</v>
       </c>
       <c r="R112" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="S112" t="s">
         <v>57</v>
@@ -9289,13 +9292,13 @@
         <v>932132</v>
       </c>
       <c r="C113" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D113" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E113" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F113" s="6">
         <v>20</v>
@@ -9334,7 +9337,7 @@
         <v>55</v>
       </c>
       <c r="R113" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="S113" t="s">
         <v>57</v>
@@ -9354,13 +9357,13 @@
         <v>1011877</v>
       </c>
       <c r="C114" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D114" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E114" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F114" s="6">
         <v>14.5</v>
@@ -9399,7 +9402,7 @@
         <v>55</v>
       </c>
       <c r="R114" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="S114" t="s">
         <v>57</v>
@@ -9419,13 +9422,13 @@
         <v>1061161</v>
       </c>
       <c r="C115" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D115" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E115" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F115" s="6">
         <v>14.5</v>
@@ -9464,7 +9467,7 @@
         <v>55</v>
       </c>
       <c r="R115" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="S115" t="s">
         <v>57</v>
@@ -9484,13 +9487,13 @@
         <v>1019999</v>
       </c>
       <c r="C116" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D116" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E116" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F116" s="6">
         <v>14.5</v>
@@ -9529,7 +9532,7 @@
         <v>55</v>
       </c>
       <c r="R116" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="S116" t="s">
         <v>57</v>
@@ -9549,13 +9552,13 @@
         <v>840822</v>
       </c>
       <c r="C117" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D117" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E117" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F117" s="6">
         <v>20</v>
@@ -9594,7 +9597,7 @@
         <v>55</v>
       </c>
       <c r="R117" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="S117" t="s">
         <v>57</v>
@@ -9614,13 +9617,13 @@
         <v>913653</v>
       </c>
       <c r="C118" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D118" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E118" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F118" s="6">
         <v>15</v>
@@ -9659,7 +9662,7 @@
         <v>55</v>
       </c>
       <c r="R118" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="S118" t="s">
         <v>57</v>
@@ -9679,13 +9682,13 @@
         <v>818963</v>
       </c>
       <c r="C119" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D119" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E119" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F119" s="6">
         <v>20</v>
@@ -9724,7 +9727,7 @@
         <v>55</v>
       </c>
       <c r="R119" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="S119" t="s">
         <v>57</v>
@@ -9744,13 +9747,13 @@
         <v>871143</v>
       </c>
       <c r="C120" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D120" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E120" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F120" s="6">
         <v>20</v>
@@ -9789,7 +9792,7 @@
         <v>55</v>
       </c>
       <c r="R120" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="S120" t="s">
         <v>55</v>
@@ -9809,13 +9812,13 @@
         <v>913648</v>
       </c>
       <c r="C121" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D121" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E121" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F121" s="6">
         <v>24</v>
@@ -9854,7 +9857,7 @@
         <v>55</v>
       </c>
       <c r="R121" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="S121" t="s">
         <v>57</v>
@@ -9874,13 +9877,13 @@
         <v>805663</v>
       </c>
       <c r="C122" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D122" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E122" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F122" s="6">
         <v>20</v>
@@ -9919,7 +9922,7 @@
         <v>55</v>
       </c>
       <c r="R122" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S122" t="s">
         <v>57</v>
@@ -9939,13 +9942,13 @@
         <v>941045</v>
       </c>
       <c r="C123" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D123" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E123" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F123" s="6">
         <v>10</v>
@@ -9984,7 +9987,7 @@
         <v>55</v>
       </c>
       <c r="R123" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S123" t="s">
         <v>57</v>
@@ -10004,13 +10007,13 @@
         <v>929464</v>
       </c>
       <c r="C124" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D124" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E124" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F124" s="6">
         <v>16</v>
@@ -10049,7 +10052,7 @@
         <v>55</v>
       </c>
       <c r="R124" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="S124" t="s">
         <v>57</v>
@@ -10069,13 +10072,13 @@
         <v>805665</v>
       </c>
       <c r="C125" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D125" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E125" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F125" s="6">
         <v>10</v>
@@ -10114,7 +10117,7 @@
         <v>55</v>
       </c>
       <c r="R125" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="S125" t="s">
         <v>57</v>
@@ -10134,13 +10137,13 @@
         <v>900310</v>
       </c>
       <c r="C126" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D126" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E126" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F126" s="6">
         <v>22</v>
@@ -10179,7 +10182,7 @@
         <v>55</v>
       </c>
       <c r="R126" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="S126" t="s">
         <v>57</v>
@@ -10199,13 +10202,13 @@
         <v>1011872</v>
       </c>
       <c r="C127" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D127" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E127" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F127" s="6">
         <v>20</v>
@@ -10244,7 +10247,7 @@
         <v>55</v>
       </c>
       <c r="R127" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S127" t="s">
         <v>57</v>
@@ -10264,13 +10267,13 @@
         <v>913650</v>
       </c>
       <c r="C128" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D128" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E128" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F128" s="6">
         <v>20</v>
@@ -10309,7 +10312,7 @@
         <v>55</v>
       </c>
       <c r="R128" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="S128" t="s">
         <v>57</v>
@@ -10329,13 +10332,13 @@
         <v>911651</v>
       </c>
       <c r="C129" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D129" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E129" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F129" s="6">
         <v>16.6</v>
@@ -10374,7 +10377,7 @@
         <v>57</v>
       </c>
       <c r="R129" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="S129" t="s">
         <v>55</v>
@@ -10394,13 +10397,13 @@
         <v>911647</v>
       </c>
       <c r="C130" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D130" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E130" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F130" s="6">
         <v>20.77</v>
@@ -10439,7 +10442,7 @@
         <v>57</v>
       </c>
       <c r="R130" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="S130" t="s">
         <v>55</v>
@@ -10459,13 +10462,13 @@
         <v>911648</v>
       </c>
       <c r="C131" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D131" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E131" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F131" s="6">
         <v>21.88</v>
@@ -10504,7 +10507,7 @@
         <v>57</v>
       </c>
       <c r="R131" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="S131" t="s">
         <v>55</v>
@@ -10524,13 +10527,13 @@
         <v>957423</v>
       </c>
       <c r="C132" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D132" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E132" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F132" s="6">
         <v>19.23</v>
@@ -10569,7 +10572,7 @@
         <v>57</v>
       </c>
       <c r="R132" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="S132" t="s">
         <v>55</v>
@@ -10589,13 +10592,13 @@
         <v>957424</v>
       </c>
       <c r="C133" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D133" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E133" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F133" s="6">
         <v>21.88</v>
@@ -10634,7 +10637,7 @@
         <v>57</v>
       </c>
       <c r="R133" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="S133" t="s">
         <v>55</v>
@@ -10654,13 +10657,13 @@
         <v>936388</v>
       </c>
       <c r="C134" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D134" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E134" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F134" s="6">
         <v>16.6</v>
@@ -10699,7 +10702,7 @@
         <v>57</v>
       </c>
       <c r="R134" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="S134" t="s">
         <v>55</v>
@@ -10719,13 +10722,13 @@
         <v>936387</v>
       </c>
       <c r="C135" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D135" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E135" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F135" s="6">
         <v>20.77</v>
@@ -10764,7 +10767,7 @@
         <v>57</v>
       </c>
       <c r="R135" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="S135" t="s">
         <v>55</v>
@@ -10784,13 +10787,13 @@
         <v>824228</v>
       </c>
       <c r="C136" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D136" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E136" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F136" s="6">
         <v>21.89</v>
@@ -10829,7 +10832,7 @@
         <v>57</v>
       </c>
       <c r="R136" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="S136" t="s">
         <v>55</v>
@@ -10849,13 +10852,13 @@
         <v>866256</v>
       </c>
       <c r="C137" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D137" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E137" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F137" s="6">
         <v>16.6</v>
@@ -10894,7 +10897,7 @@
         <v>57</v>
       </c>
       <c r="R137" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="S137" t="s">
         <v>55</v>
@@ -10914,13 +10917,13 @@
         <v>805464</v>
       </c>
       <c r="C138" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D138" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E138" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F138" s="6">
         <v>19.23</v>
@@ -10959,7 +10962,7 @@
         <v>57</v>
       </c>
       <c r="R138" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="S138" t="s">
         <v>55</v>
@@ -10979,13 +10982,13 @@
         <v>842611</v>
       </c>
       <c r="C139" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D139" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E139" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F139" s="6">
         <v>21.88</v>
@@ -11024,7 +11027,7 @@
         <v>57</v>
       </c>
       <c r="R139" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="S139" t="s">
         <v>55</v>
@@ -11044,13 +11047,13 @@
         <v>1015821</v>
       </c>
       <c r="C140" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D140" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E140" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F140" s="6">
         <v>13.5</v>
@@ -11089,7 +11092,7 @@
         <v>57</v>
       </c>
       <c r="R140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="S140" t="s">
         <v>55</v>
@@ -11109,13 +11112,13 @@
         <v>1015823</v>
       </c>
       <c r="C141" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E141" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F141" s="6">
         <v>15</v>
@@ -11154,7 +11157,7 @@
         <v>57</v>
       </c>
       <c r="R141" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="S141" t="s">
         <v>55</v>
@@ -11174,13 +11177,13 @@
         <v>805465</v>
       </c>
       <c r="C142" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E142" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F142" s="6">
         <v>15.38</v>
@@ -11219,7 +11222,7 @@
         <v>57</v>
       </c>
       <c r="R142" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="S142" t="s">
         <v>55</v>
@@ -11239,13 +11242,13 @@
         <v>990715</v>
       </c>
       <c r="C143" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D143" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E143" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F143" s="6">
         <v>9.23</v>
@@ -11284,7 +11287,7 @@
         <v>57</v>
       </c>
       <c r="R143" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="S143" t="s">
         <v>55</v>
@@ -11304,13 +11307,13 @@
         <v>881794</v>
       </c>
       <c r="C144" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D144" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E144" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F144" s="6">
         <v>13.85</v>
@@ -11349,7 +11352,7 @@
         <v>57</v>
       </c>
       <c r="R144" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="S144" t="s">
         <v>55</v>
@@ -11369,13 +11372,13 @@
         <v>805466</v>
       </c>
       <c r="C145" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D145" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E145" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F145" s="6">
         <v>22.66</v>
@@ -11414,7 +11417,7 @@
         <v>57</v>
       </c>
       <c r="R145" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="S145" t="s">
         <v>55</v>
@@ -11434,13 +11437,13 @@
         <v>836358</v>
       </c>
       <c r="C146" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E146" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F146" s="6">
         <v>19.23</v>
@@ -11479,7 +11482,7 @@
         <v>57</v>
       </c>
       <c r="R146" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="S146" t="s">
         <v>55</v>
@@ -11499,13 +11502,13 @@
         <v>867239</v>
       </c>
       <c r="C147" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D147" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E147" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F147" s="6">
         <v>20.77</v>
@@ -11544,7 +11547,7 @@
         <v>57</v>
       </c>
       <c r="R147" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="S147" t="s">
         <v>55</v>
@@ -11564,13 +11567,13 @@
         <v>805468</v>
       </c>
       <c r="C148" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D148" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E148" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F148" s="6">
         <v>29.62</v>
@@ -11609,7 +11612,7 @@
         <v>57</v>
       </c>
       <c r="R148" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="S148" t="s">
         <v>55</v>
@@ -11629,13 +11632,13 @@
         <v>805469</v>
       </c>
       <c r="C149" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D149" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E149" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F149" s="6">
         <v>32.69</v>
@@ -11674,7 +11677,7 @@
         <v>57</v>
       </c>
       <c r="R149" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="S149" t="s">
         <v>55</v>
@@ -11694,13 +11697,13 @@
         <v>805461</v>
       </c>
       <c r="C150" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D150" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E150" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F150" s="6">
         <v>23.08</v>
@@ -11739,7 +11742,7 @@
         <v>57</v>
       </c>
       <c r="R150" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="S150" t="s">
         <v>55</v>
@@ -11759,13 +11762,13 @@
         <v>805470</v>
       </c>
       <c r="C151" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D151" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E151" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F151" s="6">
         <v>21.54</v>
@@ -11804,7 +11807,7 @@
         <v>57</v>
       </c>
       <c r="R151" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="S151" t="s">
         <v>55</v>
@@ -11824,13 +11827,13 @@
         <v>805471</v>
       </c>
       <c r="C152" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D152" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E152" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F152" s="6">
         <v>16.92</v>
@@ -11869,7 +11872,7 @@
         <v>57</v>
       </c>
       <c r="R152" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="S152" t="s">
         <v>55</v>
@@ -11889,13 +11892,13 @@
         <v>805472</v>
       </c>
       <c r="C153" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D153" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E153" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F153" s="6">
         <v>15.38</v>
@@ -11934,7 +11937,7 @@
         <v>57</v>
       </c>
       <c r="R153" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="S153" t="s">
         <v>55</v>
@@ -11954,13 +11957,13 @@
         <v>805473</v>
       </c>
       <c r="C154" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D154" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E154" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F154" s="6">
         <v>15.38</v>
@@ -11999,7 +12002,7 @@
         <v>57</v>
       </c>
       <c r="R154" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="S154" t="s">
         <v>55</v>
@@ -12019,13 +12022,13 @@
         <v>805474</v>
       </c>
       <c r="C155" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D155" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E155" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F155" s="6">
         <v>15.38</v>
@@ -12064,7 +12067,7 @@
         <v>57</v>
       </c>
       <c r="R155" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="S155" t="s">
         <v>55</v>
@@ -12084,13 +12087,13 @@
         <v>990712</v>
       </c>
       <c r="C156" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D156" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E156" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F156" s="6">
         <v>8.92</v>
@@ -12129,7 +12132,7 @@
         <v>57</v>
       </c>
       <c r="R156" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="S156" t="s">
         <v>55</v>
@@ -12149,13 +12152,13 @@
         <v>805475</v>
       </c>
       <c r="C157" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D157" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E157" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F157" s="6">
         <v>18.46</v>
@@ -12194,7 +12197,7 @@
         <v>57</v>
       </c>
       <c r="R157" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="S157" t="s">
         <v>55</v>
@@ -12214,13 +12217,13 @@
         <v>805476</v>
       </c>
       <c r="C158" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D158" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E158" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F158" s="6">
         <v>10.77</v>
@@ -12259,7 +12262,7 @@
         <v>57</v>
       </c>
       <c r="R158" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="S158" t="s">
         <v>55</v>
@@ -12279,13 +12282,13 @@
         <v>805477</v>
       </c>
       <c r="C159" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D159" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E159" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F159" s="6">
         <v>18.46</v>
@@ -12324,7 +12327,7 @@
         <v>57</v>
       </c>
       <c r="R159" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="S159" t="s">
         <v>55</v>
@@ -12349,10 +12352,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -12360,7 +12363,7 @@
         <v>0.5412</v>
       </c>
       <c r="B2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -12368,7 +12371,7 @@
         <v>0.65</v>
       </c>
       <c r="B3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -12376,7 +12379,7 @@
         <v>0.6574</v>
       </c>
       <c r="B4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -12384,7 +12387,7 @@
         <v>0.6574</v>
       </c>
       <c r="B5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-21T11:16:02.010Z</t>
+    <t>2026-03-22T11:16:02.721Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-22T11:16:02.721Z</t>
+    <t>2026-03-23T11:16:03.068Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-23T11:16:03.068Z</t>
+    <t>2026-03-24T11:16:02.890Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-24T11:16:02.890Z</t>
+    <t>2026-03-25T11:16:02.493Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-25T11:16:02.493Z</t>
+    <t>2026-03-26T11:16:02.817Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-26T11:16:02.817Z</t>
+    <t>2026-03-27T11:16:02.469Z</t>
   </si>
   <si>
     <t>Environment</t>
@@ -2255,10 +2255,10 @@
         <v>62</v>
       </c>
       <c r="S4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U4" t="s">
         <v>55</v>
@@ -2840,10 +2840,10 @@
         <v>87</v>
       </c>
       <c r="S13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" t="s">
         <v>55</v>
@@ -3363,7 +3363,7 @@
         <v>55</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U21" t="s">
         <v>55</v>
@@ -3555,13 +3555,13 @@
         <v>117</v>
       </c>
       <c r="S24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3883,7 +3883,7 @@
         <v>55</v>
       </c>
       <c r="T29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="s">
         <v>55</v>
@@ -4208,7 +4208,7 @@
         <v>55</v>
       </c>
       <c r="T34">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="U34" t="s">
         <v>55</v>
@@ -4338,7 +4338,7 @@
         <v>55</v>
       </c>
       <c r="T36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U36" t="s">
         <v>55</v>
@@ -4400,13 +4400,13 @@
         <v>153</v>
       </c>
       <c r="S37" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U37" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -4663,7 +4663,7 @@
         <v>55</v>
       </c>
       <c r="T41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U41" t="s">
         <v>55</v>
@@ -4790,13 +4790,13 @@
         <v>167</v>
       </c>
       <c r="S43" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T43">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U43" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -5183,7 +5183,7 @@
         <v>55</v>
       </c>
       <c r="T49">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="U49" t="s">
         <v>55</v>
@@ -5248,7 +5248,7 @@
         <v>55</v>
       </c>
       <c r="T50">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U50" t="s">
         <v>55</v>
@@ -5313,7 +5313,7 @@
         <v>55</v>
       </c>
       <c r="T51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U51" t="s">
         <v>55</v>
@@ -5443,7 +5443,7 @@
         <v>55</v>
       </c>
       <c r="T53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U53" t="s">
         <v>55</v>
@@ -6223,7 +6223,7 @@
         <v>57</v>
       </c>
       <c r="T65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U65" t="s">
         <v>55</v>
@@ -8755,10 +8755,10 @@
         <v>321</v>
       </c>
       <c r="S104" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U104" t="s">
         <v>55</v>
@@ -9080,10 +9080,10 @@
         <v>335</v>
       </c>
       <c r="S109" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U109" t="s">
         <v>55</v>
@@ -9798,7 +9798,7 @@
         <v>55</v>
       </c>
       <c r="T120">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U120" t="s">
         <v>55</v>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-27T11:16:02.469Z</t>
+    <t>2026-03-28T11:16:03.029Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-28T11:16:03.029Z</t>
+    <t>2026-03-29T11:16:03.090Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-29T11:16:03.090Z</t>
+    <t>2026-03-30T11:16:02.757Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-30T11:16:02.757Z</t>
+    <t>2026-03-31T11:16:03.120Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-03-31T11:16:03.120Z</t>
+    <t>2026-04-01T11:16:02.514Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-04-01T11:16:02.514Z</t>
+    <t>2026-04-02T11:16:02.842Z</t>
   </si>
   <si>
     <t>Environment</t>

--- a/docs/masterPriceList.xlsx
+++ b/docs/masterPriceList.xlsx
@@ -27,7 +27,7 @@
     <t>Sync time (UTC)</t>
   </si>
   <si>
-    <t>2026-04-02T11:16:02.842Z</t>
+    <t>2026-04-03T11:16:03.226Z</t>
   </si>
   <si>
     <t>Environment</t>
@@ -2258,7 +2258,7 @@
         <v>55</v>
       </c>
       <c r="T4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U4" t="s">
         <v>55</v>
@@ -2843,7 +2843,7 @@
         <v>55</v>
       </c>
       <c r="T13">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U13" t="s">
         <v>55</v>
@@ -3363,7 +3363,7 @@
         <v>55</v>
       </c>
       <c r="T21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U21" t="s">
         <v>55</v>
@@ -3558,7 +3558,7 @@
         <v>55</v>
       </c>
       <c r="T24">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U24" t="s">
         <v>55</v>
@@ -4208,7 +4208,7 @@
         <v>55</v>
       </c>
       <c r="T34">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="U34" t="s">
         <v>55</v>
@@ -4338,7 +4338,7 @@
         <v>55</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U36" t="s">
         <v>55</v>
@@ -4400,13 +4400,13 @@
         <v>153</v>
       </c>
       <c r="S37" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -4468,7 +4468,7 @@
         <v>55</v>
       </c>
       <c r="T38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U38" t="s">
         <v>55</v>
@@ -4660,13 +4660,13 @@
         <v>163</v>
       </c>
       <c r="S41" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U41" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -5183,7 +5183,7 @@
         <v>55</v>
       </c>
       <c r="T49">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="U49" t="s">
         <v>55</v>
@@ -5245,13 +5245,13 @@
         <v>184</v>
       </c>
       <c r="S50" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U50" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -5310,13 +5310,13 @@
         <v>188</v>
       </c>
       <c r="S51" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U51" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -6226,7 +6226,7 @@
         <v>4</v>
       </c>
       <c r="U65" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -6285,10 +6285,10 @@
         <v>224</v>
       </c>
       <c r="S66" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U66" t="s">
         <v>55</v>
@@ -6743,7 +6743,7 @@
         <v>55</v>
       </c>
       <c r="T73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U73" t="s">
         <v>55</v>
@@ -8758,7 +8758,7 @@
         <v>55</v>
       </c>
       <c r="T104">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="U104" t="s">
         <v>55</v>
@@ -9795,10 +9795,10 @@
         <v>358</v>
       </c>
       <c r="S120" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T120">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U120" t="s">
         <v>55</v>
